--- a/research/traditional_assets/database/data/singapore/singapore_office_equipment_services.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_office_equipment_services.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07907719695391871</v>
+        <v>0.07898011571909706</v>
       </c>
       <c r="C2">
-        <v>104.5125765167572</v>
+        <v>103.7538738076576</v>
       </c>
       <c r="D2">
-        <v>101.9425765167572</v>
+        <v>102.2355923111152</v>
       </c>
       <c r="E2">
-        <v>-6.571850345752963</v>
+        <v>-5.520131842295433</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.05171850345753</v>
       </c>
       <c r="G2">
         <v>2.57</v>
@@ -1439,28 +1439,28 @@
         <v>4.19</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.05290144072391374</v>
       </c>
       <c r="N2">
-        <v>4.19</v>
+        <v>4.137098559276086</v>
       </c>
       <c r="O2">
-        <v>0.7122999999999999</v>
+        <v>0.7033067550769346</v>
       </c>
       <c r="P2">
-        <v>3.4777</v>
+        <v>3.433791804199151</v>
       </c>
       <c r="Q2">
-        <v>3.8777</v>
+        <v>3.833791804199151</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07907719695391871</v>
+        <v>0.07935618759504753</v>
       </c>
       <c r="T2">
-        <v>0.7685264885431575</v>
+        <v>0.7749696904168022</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>79.20389204269702</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07898011571909706</v>
+        <v>0.0788830344842754</v>
       </c>
       <c r="C3">
-        <v>103.7538738076576</v>
+        <v>102.9968603976585</v>
       </c>
       <c r="D3">
-        <v>102.2355923111152</v>
+        <v>102.5302974045736</v>
       </c>
       <c r="E3">
-        <v>-5.520131842295433</v>
+        <v>-4.468413338837903</v>
       </c>
       <c r="F3">
-        <v>1.05171850345753</v>
+        <v>2.103437006915059</v>
       </c>
       <c r="G3">
         <v>2.57</v>
@@ -1521,28 +1521,28 @@
         <v>4.19</v>
       </c>
       <c r="M3">
-        <v>0.05290144072391374</v>
+        <v>0.1058028814478275</v>
       </c>
       <c r="N3">
-        <v>4.137098559276086</v>
+        <v>4.084197118552172</v>
       </c>
       <c r="O3">
-        <v>0.7033067550769346</v>
+        <v>0.6943135101538693</v>
       </c>
       <c r="P3">
-        <v>3.433791804199151</v>
+        <v>3.389883608398303</v>
       </c>
       <c r="Q3">
-        <v>3.833791804199151</v>
+        <v>3.789883608398303</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07935618759504753</v>
+        <v>0.07964087192273001</v>
       </c>
       <c r="T3">
-        <v>0.7749696904168022</v>
+        <v>0.7815443862062356</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>79.20389204269702</v>
+        <v>39.60194602134852</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0788830344842754</v>
+        <v>0.07878595324945374</v>
       </c>
       <c r="C4">
-        <v>102.9968603976585</v>
+        <v>102.2415509377521</v>
       </c>
       <c r="D4">
-        <v>102.5302974045736</v>
+        <v>102.8267064481247</v>
       </c>
       <c r="E4">
-        <v>-4.468413338837903</v>
+        <v>-3.416694835380374</v>
       </c>
       <c r="F4">
-        <v>2.103437006915059</v>
+        <v>3.155155510372589</v>
       </c>
       <c r="G4">
         <v>2.57</v>
@@ -1603,28 +1603,28 @@
         <v>4.19</v>
       </c>
       <c r="M4">
-        <v>0.1058028814478275</v>
+        <v>0.1587043221717412</v>
       </c>
       <c r="N4">
-        <v>4.084197118552172</v>
+        <v>4.031295677828258</v>
       </c>
       <c r="O4">
-        <v>0.6943135101538693</v>
+        <v>0.685320265230804</v>
       </c>
       <c r="P4">
-        <v>3.389883608398303</v>
+        <v>3.345975412597455</v>
       </c>
       <c r="Q4">
-        <v>3.789883608398303</v>
+        <v>3.745975412597455</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07964087192273001</v>
+        <v>0.07993142603036468</v>
       </c>
       <c r="T4">
-        <v>0.7815443862062356</v>
+        <v>0.7882546427335952</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>39.60194602134852</v>
+        <v>26.40129734756567</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07878595324945374</v>
+        <v>0.07868887201463207</v>
       </c>
       <c r="C5">
-        <v>102.2415509377521</v>
+        <v>101.4879602488424</v>
       </c>
       <c r="D5">
-        <v>102.8267064481247</v>
+        <v>103.1248342626725</v>
       </c>
       <c r="E5">
-        <v>-3.416694835380374</v>
+        <v>-2.364976331922844</v>
       </c>
       <c r="F5">
-        <v>3.155155510372589</v>
+        <v>4.206874013830118</v>
       </c>
       <c r="G5">
         <v>2.57</v>
@@ -1685,28 +1685,28 @@
         <v>4.19</v>
       </c>
       <c r="M5">
-        <v>0.1587043221717412</v>
+        <v>0.2116057628956549</v>
       </c>
       <c r="N5">
-        <v>4.031295677828258</v>
+        <v>3.978394237104344</v>
       </c>
       <c r="O5">
-        <v>0.685320265230804</v>
+        <v>0.6763270203077386</v>
       </c>
       <c r="P5">
-        <v>3.345975412597455</v>
+        <v>3.302067216796606</v>
       </c>
       <c r="Q5">
-        <v>3.745975412597455</v>
+        <v>3.702067216796606</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07993142603036468</v>
+        <v>0.08022803334857508</v>
       </c>
       <c r="T5">
-        <v>0.7882546427335952</v>
+        <v>0.7951046962719418</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>26.40129734756567</v>
+        <v>19.80097301067426</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07868887201463207</v>
+        <v>0.07859179077981042</v>
       </c>
       <c r="C6">
-        <v>101.4879602488424</v>
+        <v>100.7361033242155</v>
       </c>
       <c r="D6">
-        <v>103.1248342626725</v>
+        <v>103.4246958415032</v>
       </c>
       <c r="E6">
-        <v>-2.364976331922844</v>
+        <v>-1.313257828465314</v>
       </c>
       <c r="F6">
-        <v>4.206874013830118</v>
+        <v>5.258592517287648</v>
       </c>
       <c r="G6">
         <v>2.57</v>
@@ -1767,28 +1767,28 @@
         <v>4.19</v>
       </c>
       <c r="M6">
-        <v>0.2116057628956549</v>
+        <v>0.2645072036195687</v>
       </c>
       <c r="N6">
-        <v>3.978394237104344</v>
+        <v>3.925492796380431</v>
       </c>
       <c r="O6">
-        <v>0.6763270203077386</v>
+        <v>0.6673337753846733</v>
       </c>
       <c r="P6">
-        <v>3.302067216796606</v>
+        <v>3.258159020995757</v>
       </c>
       <c r="Q6">
-        <v>3.702067216796606</v>
+        <v>3.658159020995758</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08022803334857508</v>
+        <v>0.08053088503137938</v>
       </c>
       <c r="T6">
-        <v>0.7951046962719418</v>
+        <v>0.8020989614637271</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>19.80097301067426</v>
+        <v>15.8407784085394</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07859179077981042</v>
+        <v>0.07849470954498874</v>
       </c>
       <c r="C7">
-        <v>100.7361033242155</v>
+        <v>99.98599533205358</v>
       </c>
       <c r="D7">
-        <v>103.4246958415032</v>
+        <v>103.7263063527988</v>
       </c>
       <c r="E7">
-        <v>-1.313257828465314</v>
+        <v>-0.2615393250077851</v>
       </c>
       <c r="F7">
-        <v>5.258592517287648</v>
+        <v>6.310311020745178</v>
       </c>
       <c r="G7">
         <v>2.57</v>
@@ -1849,28 +1849,28 @@
         <v>4.19</v>
       </c>
       <c r="M7">
-        <v>0.2645072036195687</v>
+        <v>0.3174086443434824</v>
       </c>
       <c r="N7">
-        <v>3.925492796380431</v>
+        <v>3.872591355656517</v>
       </c>
       <c r="O7">
-        <v>0.6673337753846733</v>
+        <v>0.6583405304616079</v>
       </c>
       <c r="P7">
-        <v>3.258159020995757</v>
+        <v>3.214250825194909</v>
       </c>
       <c r="Q7">
-        <v>3.658159020995758</v>
+        <v>3.614250825194909</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08053088503137938</v>
+        <v>0.08084018036700931</v>
       </c>
       <c r="T7">
-        <v>0.8020989614637271</v>
+        <v>0.8092420408085291</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>15.8407784085394</v>
+        <v>13.20064867378284</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07849470954498874</v>
+        <v>0.07848477831016709</v>
       </c>
       <c r="C8">
-        <v>99.98599533205358</v>
+        <v>98.9652302509156</v>
       </c>
       <c r="D8">
-        <v>103.7263063527988</v>
+        <v>103.7572597751183</v>
       </c>
       <c r="E8">
-        <v>-0.2615393250077851</v>
+        <v>0.7901791784497441</v>
       </c>
       <c r="F8">
-        <v>6.310311020745178</v>
+        <v>7.362029524202707</v>
       </c>
       <c r="G8">
         <v>2.57</v>
@@ -1931,45 +1931,45 @@
         <v>4.19</v>
       </c>
       <c r="M8">
-        <v>0.3174086443434824</v>
+        <v>0.3813531293537002</v>
       </c>
       <c r="N8">
-        <v>3.872591355656517</v>
+        <v>3.808646870646299</v>
       </c>
       <c r="O8">
-        <v>0.6583405304616079</v>
+        <v>0.647469968009871</v>
       </c>
       <c r="P8">
-        <v>3.214250825194909</v>
+        <v>3.161176902636428</v>
       </c>
       <c r="Q8">
-        <v>3.614250825194909</v>
+        <v>3.561176902636429</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08084018036700931</v>
+        <v>0.08115612721523344</v>
       </c>
       <c r="T8">
-        <v>0.8092420408085291</v>
+        <v>0.8165387347628967</v>
       </c>
       <c r="U8">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V8">
         <v>0.17</v>
       </c>
       <c r="W8">
-        <v>0.04174899999999999</v>
+        <v>0.042994</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>13.20064867378284</v>
+        <v>10.98719186361738</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07848477831016709</v>
+        <v>0.07851302707534542</v>
       </c>
       <c r="C9">
-        <v>98.9652302509156</v>
+        <v>97.82551512776755</v>
       </c>
       <c r="D9">
-        <v>103.7572597751183</v>
+        <v>103.6692631554278</v>
       </c>
       <c r="E9">
-        <v>0.7901791784497449</v>
+        <v>1.841897681907274</v>
       </c>
       <c r="F9">
-        <v>7.362029524202708</v>
+        <v>8.413748027660237</v>
       </c>
       <c r="G9">
         <v>2.57</v>
@@ -2013,45 +2013,45 @@
         <v>4.19</v>
       </c>
       <c r="M9">
-        <v>0.3813531293537002</v>
+        <v>0.4501355194798227</v>
       </c>
       <c r="N9">
-        <v>3.808646870646299</v>
+        <v>3.739864480520177</v>
       </c>
       <c r="O9">
-        <v>0.647469968009871</v>
+        <v>0.6357769616884301</v>
       </c>
       <c r="P9">
-        <v>3.161176902636428</v>
+        <v>3.104087518831747</v>
       </c>
       <c r="Q9">
-        <v>3.561176902636429</v>
+        <v>3.504087518831747</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08115612721523344</v>
+        <v>0.08147894247320155</v>
       </c>
       <c r="T9">
-        <v>0.8165387347628967</v>
+        <v>0.823994052498881</v>
       </c>
       <c r="U9">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V9">
         <v>0.17</v>
       </c>
       <c r="W9">
-        <v>0.042994</v>
+        <v>0.044405</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y9">
-        <v>10.98719186361737</v>
+        <v>9.308307873242196</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07851302707534542</v>
+        <v>0.07844250584052376</v>
       </c>
       <c r="C10">
-        <v>97.82551512776755</v>
+        <v>96.99375394615402</v>
       </c>
       <c r="D10">
-        <v>103.6692631554278</v>
+        <v>103.8892204772718</v>
       </c>
       <c r="E10">
-        <v>1.841897681907274</v>
+        <v>2.893616185364803</v>
       </c>
       <c r="F10">
-        <v>8.413748027660237</v>
+        <v>9.465466531117766</v>
       </c>
       <c r="G10">
         <v>2.57</v>
@@ -2095,28 +2095,28 @@
         <v>4.19</v>
       </c>
       <c r="M10">
-        <v>0.4501355194798227</v>
+        <v>0.5064024594148004</v>
       </c>
       <c r="N10">
-        <v>3.739864480520177</v>
+        <v>3.683597540585199</v>
       </c>
       <c r="O10">
-        <v>0.6357769616884301</v>
+        <v>0.6262115818994839</v>
       </c>
       <c r="P10">
-        <v>3.104087518831747</v>
+        <v>3.057385958685715</v>
       </c>
       <c r="Q10">
-        <v>3.504087518831747</v>
+        <v>3.457385958685716</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08147894247320155</v>
+        <v>0.08180885257200413</v>
       </c>
       <c r="T10">
-        <v>0.823994052498881</v>
+        <v>0.83161322337192</v>
       </c>
       <c r="U10">
         <v>0.0535</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>9.308307873242196</v>
+        <v>8.274051442881953</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07844250584052376</v>
+        <v>0.0784383846057021</v>
       </c>
       <c r="C11">
-        <v>96.99375394615402</v>
+        <v>95.9549185375448</v>
       </c>
       <c r="D11">
-        <v>103.8892204772718</v>
+        <v>103.9021035721201</v>
       </c>
       <c r="E11">
-        <v>2.893616185364803</v>
+        <v>3.945334688822332</v>
       </c>
       <c r="F11">
-        <v>9.465466531117766</v>
+        <v>10.5171850345753</v>
       </c>
       <c r="G11">
         <v>2.57</v>
@@ -2177,45 +2177,45 @@
         <v>4.19</v>
       </c>
       <c r="M11">
-        <v>0.5064024594148004</v>
+        <v>0.5710831473774385</v>
       </c>
       <c r="N11">
-        <v>3.683597540585199</v>
+        <v>3.618916852622561</v>
       </c>
       <c r="O11">
-        <v>0.6262115818994839</v>
+        <v>0.6152158649458355</v>
       </c>
       <c r="P11">
-        <v>3.057385958685715</v>
+        <v>3.003700987676726</v>
       </c>
       <c r="Q11">
-        <v>3.457385958685716</v>
+        <v>3.403700987676726</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08180885257200413</v>
+        <v>0.08214609400633567</v>
       </c>
       <c r="T11">
-        <v>0.83161322337192</v>
+        <v>0.8394017091532487</v>
       </c>
       <c r="U11">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V11">
         <v>0.17</v>
       </c>
       <c r="W11">
-        <v>0.044405</v>
+        <v>0.045069</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y11">
-        <v>8.274051442881953</v>
+        <v>7.336935119240628</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0784383846057021</v>
+        <v>0.07837450337088044</v>
       </c>
       <c r="C12">
-        <v>95.9549185375448</v>
+        <v>95.10330395442611</v>
       </c>
       <c r="D12">
-        <v>103.9021035721201</v>
+        <v>104.1022074924589</v>
       </c>
       <c r="E12">
-        <v>3.945334688822334</v>
+        <v>4.997053192279863</v>
       </c>
       <c r="F12">
-        <v>10.5171850345753</v>
+        <v>11.56890353803283</v>
       </c>
       <c r="G12">
         <v>2.57</v>
@@ -2259,28 +2259,28 @@
         <v>4.19</v>
       </c>
       <c r="M12">
-        <v>0.5710831473774386</v>
+        <v>0.6281914621151825</v>
       </c>
       <c r="N12">
-        <v>3.618916852622561</v>
+        <v>3.561808537884817</v>
       </c>
       <c r="O12">
-        <v>0.6152158649458355</v>
+        <v>0.6055074514404188</v>
       </c>
       <c r="P12">
-        <v>3.003700987676726</v>
+        <v>2.956301086444398</v>
       </c>
       <c r="Q12">
-        <v>3.403700987676726</v>
+        <v>3.356301086444399</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08214609400633567</v>
+        <v>0.08249091389986565</v>
       </c>
       <c r="T12">
-        <v>0.8394017091532487</v>
+        <v>0.8473652170869668</v>
       </c>
       <c r="U12">
         <v>0.0543</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>7.336935119240627</v>
+        <v>6.669941017491477</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07837450337088044</v>
+        <v>0.07831062213605879</v>
       </c>
       <c r="C13">
-        <v>95.10330395442611</v>
+        <v>94.25246161444777</v>
       </c>
       <c r="D13">
-        <v>104.1022074924589</v>
+        <v>104.3030836559381</v>
       </c>
       <c r="E13">
-        <v>4.997053192279863</v>
+        <v>6.048771695737392</v>
       </c>
       <c r="F13">
-        <v>11.56890353803283</v>
+        <v>12.62062204149036</v>
       </c>
       <c r="G13">
         <v>2.57</v>
@@ -2341,28 +2341,28 @@
         <v>4.19</v>
       </c>
       <c r="M13">
-        <v>0.6281914621151825</v>
+        <v>0.6852997768529263</v>
       </c>
       <c r="N13">
-        <v>3.561808537884817</v>
+        <v>3.504700223147073</v>
       </c>
       <c r="O13">
-        <v>0.6055074514404188</v>
+        <v>0.5957990379350024</v>
       </c>
       <c r="P13">
-        <v>2.956301086444398</v>
+        <v>2.908901185212071</v>
       </c>
       <c r="Q13">
-        <v>3.356301086444399</v>
+        <v>3.308901185212071</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08249091389986565</v>
+        <v>0.0828435706091577</v>
       </c>
       <c r="T13">
-        <v>0.8473652170869668</v>
+        <v>0.8555097138373604</v>
       </c>
       <c r="U13">
         <v>0.0543</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>6.669941017491477</v>
+        <v>6.114112599367188</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07831062213605879</v>
+        <v>0.07835464090123712</v>
       </c>
       <c r="C14">
-        <v>94.25246161444777</v>
+        <v>93.06224205095747</v>
       </c>
       <c r="D14">
-        <v>104.3030836559381</v>
+        <v>104.1645825959054</v>
       </c>
       <c r="E14">
-        <v>6.048771695737392</v>
+        <v>7.100490199194922</v>
       </c>
       <c r="F14">
-        <v>12.62062204149036</v>
+        <v>13.67234054494788</v>
       </c>
       <c r="G14">
         <v>2.57</v>
@@ -2423,45 +2423,45 @@
         <v>4.19</v>
       </c>
       <c r="M14">
-        <v>0.6852997768529263</v>
+        <v>0.756080432135618</v>
       </c>
       <c r="N14">
-        <v>3.504700223147073</v>
+        <v>3.433919567864382</v>
       </c>
       <c r="O14">
-        <v>0.5957990379350024</v>
+        <v>0.5837663265369449</v>
       </c>
       <c r="P14">
-        <v>2.908901185212071</v>
+        <v>2.850153241327437</v>
       </c>
       <c r="Q14">
-        <v>3.308901185212071</v>
+        <v>3.250153241327437</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0828435706091577</v>
+        <v>0.08320433436923806</v>
       </c>
       <c r="T14">
-        <v>0.8555097138373604</v>
+        <v>0.8638414403981077</v>
       </c>
       <c r="U14">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V14">
         <v>0.17</v>
       </c>
       <c r="W14">
-        <v>0.045069</v>
+        <v>0.045899</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y14">
-        <v>6.114112599367188</v>
+        <v>5.541738447277313</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07835464090123712</v>
+        <v>0.07829905966641547</v>
       </c>
       <c r="C15">
-        <v>93.06224205095747</v>
+        <v>92.18546597158249</v>
       </c>
       <c r="D15">
-        <v>104.1645825959054</v>
+        <v>104.3395250199879</v>
       </c>
       <c r="E15">
-        <v>7.100490199194922</v>
+        <v>8.152208702652452</v>
       </c>
       <c r="F15">
-        <v>13.67234054494788</v>
+        <v>14.72405904840542</v>
       </c>
       <c r="G15">
         <v>2.57</v>
@@ -2505,28 +2505,28 @@
         <v>4.19</v>
       </c>
       <c r="M15">
-        <v>0.756080432135618</v>
+        <v>0.8142404653768195</v>
       </c>
       <c r="N15">
-        <v>3.433919567864382</v>
+        <v>3.37575953462318</v>
       </c>
       <c r="O15">
-        <v>0.5837663265369449</v>
+        <v>0.5738791208859406</v>
       </c>
       <c r="P15">
-        <v>2.850153241327437</v>
+        <v>2.801880413737239</v>
       </c>
       <c r="Q15">
-        <v>3.250153241327437</v>
+        <v>3.20188041373724</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08320433436923806</v>
+        <v>0.08357348798420403</v>
       </c>
       <c r="T15">
-        <v>0.8638414403981077</v>
+        <v>0.8723669280416633</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.541738447277313</v>
+        <v>5.145899986757504</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07829905966641547</v>
+        <v>0.07824347843159379</v>
       </c>
       <c r="C16">
-        <v>92.18546597158249</v>
+        <v>91.30927850568278</v>
       </c>
       <c r="D16">
-        <v>104.3395250199879</v>
+        <v>104.5150560575457</v>
       </c>
       <c r="E16">
-        <v>8.152208702652452</v>
+        <v>9.203927206109984</v>
       </c>
       <c r="F16">
-        <v>14.72405904840542</v>
+        <v>15.77577755186295</v>
       </c>
       <c r="G16">
         <v>2.57</v>
@@ -2587,28 +2587,28 @@
         <v>4.19</v>
       </c>
       <c r="M16">
-        <v>0.8142404653768195</v>
+        <v>0.8724004986180209</v>
       </c>
       <c r="N16">
-        <v>3.37575953462318</v>
+        <v>3.317599501381979</v>
       </c>
       <c r="O16">
-        <v>0.5738791208859406</v>
+        <v>0.5639919152349364</v>
       </c>
       <c r="P16">
-        <v>2.801880413737239</v>
+        <v>2.753607586147042</v>
       </c>
       <c r="Q16">
-        <v>3.20188041373724</v>
+        <v>3.153607586147043</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08357348798420403</v>
+        <v>0.08395132756658094</v>
       </c>
       <c r="T16">
-        <v>0.8723669280416633</v>
+        <v>0.8810930153944788</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.145899986757504</v>
+        <v>4.802839987640337</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07824347843159379</v>
+        <v>0.07818789719677212</v>
       </c>
       <c r="C17">
-        <v>91.30927850568278</v>
+        <v>90.43368262894876</v>
       </c>
       <c r="D17">
-        <v>104.5150560575457</v>
+        <v>104.6911786842692</v>
       </c>
       <c r="E17">
-        <v>9.203927206109981</v>
+        <v>10.25564570956751</v>
       </c>
       <c r="F17">
-        <v>15.77577755186294</v>
+        <v>16.82749605532047</v>
       </c>
       <c r="G17">
         <v>2.57</v>
@@ -2669,28 +2669,28 @@
         <v>4.19</v>
       </c>
       <c r="M17">
-        <v>0.8724004986180207</v>
+        <v>0.9305605318592223</v>
       </c>
       <c r="N17">
-        <v>3.317599501381979</v>
+        <v>3.259439468140777</v>
       </c>
       <c r="O17">
-        <v>0.5639919152349365</v>
+        <v>0.5541047095839322</v>
       </c>
       <c r="P17">
-        <v>2.753607586147043</v>
+        <v>2.705334758556845</v>
       </c>
       <c r="Q17">
-        <v>3.153607586147043</v>
+        <v>3.105334758556845</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08395132756658094</v>
+        <v>0.08433816332949062</v>
       </c>
       <c r="T17">
-        <v>0.8810930153944788</v>
+        <v>0.8900268667318852</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>4.802839987640338</v>
+        <v>4.502662488412817</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07818789719677212</v>
+        <v>0.07848506596195046</v>
       </c>
       <c r="C18">
-        <v>90.43368262894876</v>
+        <v>88.44714841072303</v>
       </c>
       <c r="D18">
-        <v>104.6911786842692</v>
+        <v>103.756362969501</v>
       </c>
       <c r="E18">
-        <v>10.25564570956751</v>
+        <v>11.30736421302504</v>
       </c>
       <c r="F18">
-        <v>16.82749605532047</v>
+        <v>17.879214558778</v>
       </c>
       <c r="G18">
         <v>2.57</v>
@@ -2751,45 +2751,45 @@
         <v>4.19</v>
       </c>
       <c r="M18">
-        <v>0.9305605318592223</v>
+        <v>1.033418601497369</v>
       </c>
       <c r="N18">
-        <v>3.259439468140777</v>
+        <v>3.156581398502631</v>
       </c>
       <c r="O18">
-        <v>0.5541047095839322</v>
+        <v>0.5366188377454473</v>
       </c>
       <c r="P18">
-        <v>2.705334758556845</v>
+        <v>2.619962560757184</v>
       </c>
       <c r="Q18">
-        <v>3.105334758556845</v>
+        <v>3.019962560757184</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08433816332949062</v>
+        <v>0.08473432043608489</v>
       </c>
       <c r="T18">
-        <v>0.8900268667318852</v>
+        <v>0.8991759915954942</v>
       </c>
       <c r="U18">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V18">
         <v>0.17</v>
       </c>
       <c r="W18">
-        <v>0.045899</v>
+        <v>0.047974</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y18">
-        <v>4.502662488412817</v>
+        <v>4.054504141815245</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07848506596195046</v>
+        <v>0.0789731347271288</v>
       </c>
       <c r="C19">
-        <v>88.44714841072303</v>
+        <v>85.89579458515416</v>
       </c>
       <c r="D19">
-        <v>103.756362969501</v>
+        <v>102.2567276473897</v>
       </c>
       <c r="E19">
-        <v>11.30736421302504</v>
+        <v>12.35908271648257</v>
       </c>
       <c r="F19">
-        <v>17.879214558778</v>
+        <v>18.93093306223554</v>
       </c>
       <c r="G19">
         <v>2.57</v>
@@ -2833,45 +2833,45 @@
         <v>4.19</v>
       </c>
       <c r="M19">
-        <v>1.033418601497369</v>
+        <v>1.160466196715038</v>
       </c>
       <c r="N19">
-        <v>3.156581398502631</v>
+        <v>3.029533803284961</v>
       </c>
       <c r="O19">
-        <v>0.5366188377454473</v>
+        <v>0.5150207465584434</v>
       </c>
       <c r="P19">
-        <v>2.619962560757184</v>
+        <v>2.514513056726518</v>
       </c>
       <c r="Q19">
-        <v>3.019962560757184</v>
+        <v>2.914513056726518</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08473432043608489</v>
+        <v>0.08514013991113269</v>
       </c>
       <c r="T19">
-        <v>0.8991759915954942</v>
+        <v>0.9085482658460206</v>
       </c>
       <c r="U19">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V19">
         <v>0.17</v>
       </c>
       <c r="W19">
-        <v>0.047974</v>
+        <v>0.050879</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>4.054504141815245</v>
+        <v>3.610617880866104</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0789731347271288</v>
+        <v>0.07940891349230715</v>
       </c>
       <c r="C20">
-        <v>85.89579458515416</v>
+        <v>83.54127181610779</v>
       </c>
       <c r="D20">
-        <v>102.2567276473897</v>
+        <v>100.9539233818009</v>
       </c>
       <c r="E20">
-        <v>12.35908271648257</v>
+        <v>13.4108012199401</v>
       </c>
       <c r="F20">
-        <v>18.93093306223553</v>
+        <v>19.98265156569306</v>
       </c>
       <c r="G20">
         <v>2.57</v>
@@ -2915,45 +2915,45 @@
         <v>4.19</v>
       </c>
       <c r="M20">
-        <v>1.160466196715038</v>
+        <v>1.280887965360925</v>
       </c>
       <c r="N20">
-        <v>3.029533803284961</v>
+        <v>2.909112034639074</v>
       </c>
       <c r="O20">
-        <v>0.5150207465584434</v>
+        <v>0.4945490458886426</v>
       </c>
       <c r="P20">
-        <v>2.514513056726518</v>
+        <v>2.414562988750431</v>
       </c>
       <c r="Q20">
-        <v>2.914513056726519</v>
+        <v>2.814562988750432</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08514013991113269</v>
+        <v>0.08555597962013228</v>
       </c>
       <c r="T20">
-        <v>0.9085482658460206</v>
+        <v>0.9181519542755723</v>
       </c>
       <c r="U20">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V20">
         <v>0.17</v>
       </c>
       <c r="W20">
-        <v>0.050879</v>
+        <v>0.053203</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y20">
-        <v>3.610617880866105</v>
+        <v>3.27116821557407</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07940891349230715</v>
+        <v>0.07942637225748549</v>
       </c>
       <c r="C21">
-        <v>83.54127181610779</v>
+        <v>82.43804986247856</v>
       </c>
       <c r="D21">
-        <v>100.9539233818009</v>
+        <v>100.9024199316292</v>
       </c>
       <c r="E21">
-        <v>13.4108012199401</v>
+        <v>14.46251972339763</v>
       </c>
       <c r="F21">
-        <v>19.98265156569306</v>
+        <v>21.03437006915059</v>
       </c>
       <c r="G21">
         <v>2.57</v>
@@ -2997,28 +2997,28 @@
         <v>4.19</v>
       </c>
       <c r="M21">
-        <v>1.280887965360925</v>
+        <v>1.348303121432553</v>
       </c>
       <c r="N21">
-        <v>2.909112034639074</v>
+        <v>2.841696878567446</v>
       </c>
       <c r="O21">
-        <v>0.4945490458886426</v>
+        <v>0.4830884693564659</v>
       </c>
       <c r="P21">
-        <v>2.414562988750431</v>
+        <v>2.35860840921098</v>
       </c>
       <c r="Q21">
-        <v>2.814562988750432</v>
+        <v>2.75860840921098</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08555597962013228</v>
+        <v>0.08598221532185685</v>
       </c>
       <c r="T21">
-        <v>0.9181519542755723</v>
+        <v>0.9279957349158627</v>
       </c>
       <c r="U21">
         <v>0.0641</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.27116821557407</v>
+        <v>3.107609804795366</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07942637225748549</v>
+        <v>0.08080337102266383</v>
       </c>
       <c r="C22">
-        <v>82.43804986247856</v>
+        <v>77.48329909662145</v>
       </c>
       <c r="D22">
-        <v>100.9024199316292</v>
+        <v>96.99938766922958</v>
       </c>
       <c r="E22">
-        <v>14.46251972339763</v>
+        <v>15.51423822685516</v>
       </c>
       <c r="F22">
-        <v>21.03437006915059</v>
+        <v>22.08608857260812</v>
       </c>
       <c r="G22">
         <v>2.57</v>
@@ -3079,45 +3079,45 @@
         <v>4.19</v>
       </c>
       <c r="M22">
-        <v>1.348303121432553</v>
+        <v>1.587989768370524</v>
       </c>
       <c r="N22">
-        <v>2.841696878567446</v>
+        <v>2.602010231629476</v>
       </c>
       <c r="O22">
-        <v>0.4830884693564659</v>
+        <v>0.4423417393770109</v>
       </c>
       <c r="P22">
-        <v>2.35860840921098</v>
+        <v>2.159668492252464</v>
       </c>
       <c r="Q22">
-        <v>2.75860840921098</v>
+        <v>2.559668492252465</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08598221532185685</v>
+        <v>0.08641924180084029</v>
       </c>
       <c r="T22">
-        <v>0.9279957349158627</v>
+        <v>0.9380887251926162</v>
       </c>
       <c r="U22">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V22">
         <v>0.17</v>
       </c>
       <c r="W22">
-        <v>0.053203</v>
+        <v>0.059677</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>3.107609804795366</v>
+        <v>2.638556043279462</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08080337102266383</v>
+        <v>0.08088556978784216</v>
       </c>
       <c r="C23">
-        <v>77.48329909662145</v>
+        <v>76.20812066994569</v>
       </c>
       <c r="D23">
-        <v>96.99938766922958</v>
+        <v>96.77592774601135</v>
       </c>
       <c r="E23">
-        <v>15.51423822685516</v>
+        <v>16.56595673031269</v>
       </c>
       <c r="F23">
-        <v>22.08608857260812</v>
+        <v>23.13780707606565</v>
       </c>
       <c r="G23">
         <v>2.57</v>
@@ -3161,28 +3161,28 @@
         <v>4.19</v>
       </c>
       <c r="M23">
-        <v>1.587989768370524</v>
+        <v>1.663608328769121</v>
       </c>
       <c r="N23">
-        <v>2.602010231629476</v>
+        <v>2.526391671230879</v>
       </c>
       <c r="O23">
-        <v>0.4423417393770109</v>
+        <v>0.4294865841092495</v>
       </c>
       <c r="P23">
-        <v>2.159668492252464</v>
+        <v>2.096905087121629</v>
       </c>
       <c r="Q23">
-        <v>2.559668492252465</v>
+        <v>2.49690508712163</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08641924180084029</v>
+        <v>0.08686747408697712</v>
       </c>
       <c r="T23">
-        <v>0.9380887251926162</v>
+        <v>0.9484405100918505</v>
       </c>
       <c r="U23">
         <v>0.07190000000000001</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.638556043279462</v>
+        <v>2.51862167767585</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08088556978784216</v>
+        <v>0.0817122785530205</v>
       </c>
       <c r="C24">
-        <v>76.20812066994569</v>
+        <v>72.96492156357293</v>
       </c>
       <c r="D24">
-        <v>96.77592774601135</v>
+        <v>94.58444714309611</v>
       </c>
       <c r="E24">
-        <v>16.56595673031269</v>
+        <v>17.61767523377022</v>
       </c>
       <c r="F24">
-        <v>23.13780707606565</v>
+        <v>24.18952557952318</v>
       </c>
       <c r="G24">
         <v>2.57</v>
@@ -3243,45 +3243,45 @@
         <v>4.19</v>
       </c>
       <c r="M24">
-        <v>1.663608328769121</v>
+        <v>1.833566038927857</v>
       </c>
       <c r="N24">
-        <v>2.526391671230879</v>
+        <v>2.356433961072142</v>
       </c>
       <c r="O24">
-        <v>0.4294865841092495</v>
+        <v>0.4005937733822642</v>
       </c>
       <c r="P24">
-        <v>2.096905087121629</v>
+        <v>1.955840187689878</v>
       </c>
       <c r="Q24">
-        <v>2.49690508712163</v>
+        <v>2.355840187689878</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08686747408697712</v>
+        <v>0.08732734877015649</v>
       </c>
       <c r="T24">
-        <v>0.9484405100918505</v>
+        <v>0.9590611725209351</v>
       </c>
       <c r="U24">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V24">
         <v>0.17</v>
       </c>
       <c r="W24">
-        <v>0.059677</v>
+        <v>0.062914</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y24">
-        <v>2.51862167767585</v>
+        <v>2.285164488784937</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0817122785530205</v>
+        <v>0.08182684731819885</v>
       </c>
       <c r="C25">
-        <v>72.96492156357293</v>
+        <v>71.61730444813185</v>
       </c>
       <c r="D25">
-        <v>94.58444714309611</v>
+        <v>94.28854853111257</v>
       </c>
       <c r="E25">
-        <v>17.61767523377022</v>
+        <v>18.66939373722775</v>
       </c>
       <c r="F25">
-        <v>24.18952557952318</v>
+        <v>25.24124408298071</v>
       </c>
       <c r="G25">
         <v>2.57</v>
@@ -3325,28 +3325,28 @@
         <v>4.19</v>
       </c>
       <c r="M25">
-        <v>1.833566038927857</v>
+        <v>1.913286301489938</v>
       </c>
       <c r="N25">
-        <v>2.356433961072142</v>
+        <v>2.276713698510061</v>
       </c>
       <c r="O25">
-        <v>0.4005937733822642</v>
+        <v>0.3870413287467104</v>
       </c>
       <c r="P25">
-        <v>1.955840187689878</v>
+        <v>1.889672369763351</v>
       </c>
       <c r="Q25">
-        <v>2.355840187689878</v>
+        <v>2.289672369763351</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08732734877015649</v>
+        <v>0.08779932541868268</v>
       </c>
       <c r="T25">
-        <v>0.9590611725209351</v>
+        <v>0.9699613260665745</v>
       </c>
       <c r="U25">
         <v>0.07580000000000001</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.285164488784937</v>
+        <v>2.189949301752232</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08182684731819884</v>
+        <v>0.08194141608337718</v>
       </c>
       <c r="C26">
-        <v>71.61730444813189</v>
+        <v>70.27153294123866</v>
       </c>
       <c r="D26">
-        <v>94.28854853111261</v>
+        <v>93.9944955276769</v>
       </c>
       <c r="E26">
-        <v>18.66939373722775</v>
+        <v>19.72111224068528</v>
       </c>
       <c r="F26">
-        <v>25.24124408298071</v>
+        <v>26.29296258643824</v>
       </c>
       <c r="G26">
         <v>2.57</v>
@@ -3407,28 +3407,28 @@
         <v>4.19</v>
       </c>
       <c r="M26">
-        <v>1.913286301489938</v>
+        <v>1.993006564052019</v>
       </c>
       <c r="N26">
-        <v>2.276713698510061</v>
+        <v>2.196993435947981</v>
       </c>
       <c r="O26">
-        <v>0.3870413287467104</v>
+        <v>0.3734888841111568</v>
       </c>
       <c r="P26">
-        <v>1.889672369763351</v>
+        <v>1.823504551836824</v>
       </c>
       <c r="Q26">
-        <v>2.289672369763351</v>
+        <v>2.223504551836824</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08779932541868268</v>
+        <v>0.08828388811116956</v>
       </c>
       <c r="T26">
-        <v>0.9699613260665745</v>
+        <v>0.9811521503734311</v>
       </c>
       <c r="U26">
         <v>0.07580000000000001</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.189949301752232</v>
+        <v>2.102351329682143</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08194141608337718</v>
+        <v>0.0820559848485555</v>
       </c>
       <c r="C27">
-        <v>70.27153294123866</v>
+        <v>68.9275898291544</v>
       </c>
       <c r="D27">
-        <v>93.9944955276769</v>
+        <v>93.70227091905018</v>
       </c>
       <c r="E27">
-        <v>19.72111224068528</v>
+        <v>20.77283074414281</v>
       </c>
       <c r="F27">
-        <v>26.29296258643824</v>
+        <v>27.34468108989577</v>
       </c>
       <c r="G27">
         <v>2.57</v>
@@ -3489,28 +3489,28 @@
         <v>4.19</v>
       </c>
       <c r="M27">
-        <v>1.993006564052019</v>
+        <v>2.072726826614099</v>
       </c>
       <c r="N27">
-        <v>2.196993435947981</v>
+        <v>2.1172731733859</v>
       </c>
       <c r="O27">
-        <v>0.3734888841111568</v>
+        <v>0.3599364394756031</v>
       </c>
       <c r="P27">
-        <v>1.823504551836824</v>
+        <v>1.757336733910297</v>
       </c>
       <c r="Q27">
-        <v>2.223504551836824</v>
+        <v>2.157336733910298</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08828388811116956</v>
+        <v>0.08878154709264258</v>
       </c>
       <c r="T27">
-        <v>0.9811521503734311</v>
+        <v>0.9926454293912838</v>
       </c>
       <c r="U27">
         <v>0.07580000000000001</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.102351329682143</v>
+        <v>2.021491663155906</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0820559848485555</v>
+        <v>0.08535277361373386</v>
       </c>
       <c r="C28">
-        <v>68.9275898291544</v>
+        <v>60.18142756604656</v>
       </c>
       <c r="D28">
-        <v>93.70227091905018</v>
+        <v>86.00782715939987</v>
       </c>
       <c r="E28">
-        <v>20.77283074414281</v>
+        <v>21.82454924760034</v>
       </c>
       <c r="F28">
-        <v>27.34468108989577</v>
+        <v>28.3963995933533</v>
       </c>
       <c r="G28">
         <v>2.57</v>
@@ -3571,45 +3571,45 @@
         <v>4.19</v>
       </c>
       <c r="M28">
-        <v>2.072726826614099</v>
+        <v>2.555675963401797</v>
       </c>
       <c r="N28">
-        <v>2.1172731733859</v>
+        <v>1.634324036598203</v>
       </c>
       <c r="O28">
-        <v>0.3599364394756031</v>
+        <v>0.2778350862216944</v>
       </c>
       <c r="P28">
-        <v>1.757336733910297</v>
+        <v>1.356488950376508</v>
       </c>
       <c r="Q28">
-        <v>2.157336733910298</v>
+        <v>1.756488950376508</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08878154709264258</v>
+        <v>0.08929284056675871</v>
       </c>
       <c r="T28">
-        <v>0.9926454293912838</v>
+        <v>1.00445359276579</v>
       </c>
       <c r="U28">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V28">
         <v>0.17</v>
       </c>
       <c r="W28">
-        <v>0.062914</v>
+        <v>0.07469999999999999</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>2.021491663155906</v>
+        <v>1.639487971089572</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08535277361373386</v>
+        <v>0.08558520237891218</v>
       </c>
       <c r="C29">
-        <v>60.18142756604656</v>
+        <v>58.63465020787127</v>
       </c>
       <c r="D29">
-        <v>86.00782715939987</v>
+        <v>85.51276830468211</v>
       </c>
       <c r="E29">
-        <v>21.82454924760034</v>
+        <v>22.87626775105787</v>
       </c>
       <c r="F29">
-        <v>28.3963995933533</v>
+        <v>29.44811809681083</v>
       </c>
       <c r="G29">
         <v>2.57</v>
@@ -3653,28 +3653,28 @@
         <v>4.19</v>
       </c>
       <c r="M29">
-        <v>2.555675963401797</v>
+        <v>2.650330628712974</v>
       </c>
       <c r="N29">
-        <v>1.634324036598203</v>
+        <v>1.539669371287025</v>
       </c>
       <c r="O29">
-        <v>0.2778350862216944</v>
+        <v>0.2617437931187943</v>
       </c>
       <c r="P29">
-        <v>1.356488950376508</v>
+        <v>1.277925578168231</v>
       </c>
       <c r="Q29">
-        <v>1.756488950376508</v>
+        <v>1.677925578168231</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08929284056675871</v>
+        <v>0.08981833663737804</v>
       </c>
       <c r="T29">
-        <v>1.00445359276579</v>
+        <v>1.016589760678477</v>
       </c>
       <c r="U29">
         <v>0.09</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>1.639487971089572</v>
+        <v>1.580934829264945</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08558520237891218</v>
+        <v>0.08581763114409054</v>
       </c>
       <c r="C30">
-        <v>58.63465020787127</v>
+        <v>57.09353932583163</v>
       </c>
       <c r="D30">
-        <v>85.51276830468211</v>
+        <v>85.0233759261</v>
       </c>
       <c r="E30">
-        <v>22.87626775105787</v>
+        <v>23.9279862545154</v>
       </c>
       <c r="F30">
-        <v>29.44811809681083</v>
+        <v>30.49983660026836</v>
       </c>
       <c r="G30">
         <v>2.57</v>
@@ -3735,28 +3735,28 @@
         <v>4.19</v>
       </c>
       <c r="M30">
-        <v>2.650330628712974</v>
+        <v>2.744985294024152</v>
       </c>
       <c r="N30">
-        <v>1.539669371287025</v>
+        <v>1.445014705975847</v>
       </c>
       <c r="O30">
-        <v>0.2617437931187943</v>
+        <v>0.245652500015894</v>
       </c>
       <c r="P30">
-        <v>1.277925578168231</v>
+        <v>1.199362205959953</v>
       </c>
       <c r="Q30">
-        <v>1.677925578168231</v>
+        <v>1.599362205959953</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08981833663737804</v>
+        <v>0.09035863541421202</v>
       </c>
       <c r="T30">
-        <v>1.016589760678477</v>
+        <v>1.029067792476028</v>
       </c>
       <c r="U30">
         <v>0.09</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>1.580934829264945</v>
+        <v>1.52641983515236</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08581763114409052</v>
+        <v>0.1010692044520949</v>
       </c>
       <c r="C31">
-        <v>57.09353932583169</v>
+        <v>32.82955440634551</v>
       </c>
       <c r="D31">
-        <v>85.02337592610004</v>
+        <v>61.8111095100714</v>
       </c>
       <c r="E31">
-        <v>23.92798625451539</v>
+        <v>24.97970475797292</v>
       </c>
       <c r="F31">
-        <v>30.49983660026836</v>
+        <v>31.55155510372589</v>
       </c>
       <c r="G31">
         <v>2.57</v>
@@ -3817,45 +3817,45 @@
         <v>4.19</v>
       </c>
       <c r="M31">
-        <v>2.744985294024152</v>
+        <v>4.631768289226961</v>
       </c>
       <c r="N31">
-        <v>1.445014705975848</v>
+        <v>-0.4417682892269612</v>
       </c>
       <c r="O31">
-        <v>0.2456525000158941</v>
+        <v>-0.07510060916858341</v>
       </c>
       <c r="P31">
-        <v>1.199362205959953</v>
+        <v>-0.3666676800583778</v>
       </c>
       <c r="Q31">
-        <v>1.599362205959954</v>
+        <v>0.03333231994162256</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.090358635414212</v>
+        <v>0.09114561322952278</v>
       </c>
       <c r="T31">
-        <v>1.029067792476028</v>
+        <v>1.047242799758032</v>
       </c>
       <c r="U31">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V31">
-        <v>0.17</v>
+        <v>0.1537857585960723</v>
       </c>
       <c r="W31">
-        <v>0.07469999999999999</v>
+        <v>0.1242242506380966</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y31">
-        <v>1.52641983515236</v>
+        <v>0.9046221093886603</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1010692044520949</v>
+        <v>0.1020792044520949</v>
       </c>
       <c r="C32">
-        <v>32.82955440634551</v>
+        <v>30.6801684577268</v>
       </c>
       <c r="D32">
-        <v>61.8111095100714</v>
+        <v>60.71344206491022</v>
       </c>
       <c r="E32">
-        <v>24.97970475797292</v>
+        <v>26.03142326143045</v>
       </c>
       <c r="F32">
-        <v>31.55155510372589</v>
+        <v>32.60327360718342</v>
       </c>
       <c r="G32">
         <v>2.57</v>
@@ -3899,37 +3899,37 @@
         <v>4.19</v>
       </c>
       <c r="M32">
-        <v>4.631768289226961</v>
+        <v>4.786160565534527</v>
       </c>
       <c r="N32">
-        <v>-0.4417682892269612</v>
+        <v>-0.596160565534527</v>
       </c>
       <c r="O32">
-        <v>-0.07510060916858341</v>
+        <v>-0.1013472961408696</v>
       </c>
       <c r="P32">
-        <v>-0.3666676800583778</v>
+        <v>-0.4948132693936574</v>
       </c>
       <c r="Q32">
-        <v>0.03333231994162256</v>
+        <v>-0.09481326939365708</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09114561322952278</v>
+        <v>0.09180279602995063</v>
       </c>
       <c r="T32">
-        <v>1.047242799758032</v>
+        <v>1.062420231638583</v>
       </c>
       <c r="U32">
         <v>0.1468</v>
       </c>
       <c r="V32">
-        <v>0.1537857585960723</v>
+        <v>0.1488249276736183</v>
       </c>
       <c r="W32">
-        <v>0.1242242506380966</v>
+        <v>0.1249525006175128</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.9046221093886603</v>
+        <v>0.875440751021284</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1020792044520949</v>
+        <v>0.1030892044520949</v>
       </c>
       <c r="C33">
-        <v>30.6801684577268</v>
+        <v>28.56908793733233</v>
       </c>
       <c r="D33">
-        <v>60.71344206491022</v>
+        <v>59.65408004797327</v>
       </c>
       <c r="E33">
-        <v>26.03142326143045</v>
+        <v>27.08314176488798</v>
       </c>
       <c r="F33">
-        <v>32.60327360718342</v>
+        <v>33.65499211064095</v>
       </c>
       <c r="G33">
         <v>2.57</v>
@@ -3981,37 +3981,37 @@
         <v>4.19</v>
       </c>
       <c r="M33">
-        <v>4.786160565534527</v>
+        <v>4.940552841842091</v>
       </c>
       <c r="N33">
-        <v>-0.596160565534527</v>
+        <v>-0.7505528418420919</v>
       </c>
       <c r="O33">
-        <v>-0.1013472961408696</v>
+        <v>-0.1275939831131556</v>
       </c>
       <c r="P33">
-        <v>-0.4948132693936574</v>
+        <v>-0.6229588587289363</v>
       </c>
       <c r="Q33">
-        <v>-0.09481326939365708</v>
+        <v>-0.2229588587289359</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09180279602995063</v>
+        <v>0.09247930773627341</v>
       </c>
       <c r="T33">
-        <v>1.062420231638583</v>
+        <v>1.078044058574444</v>
       </c>
       <c r="U33">
         <v>0.1468</v>
       </c>
       <c r="V33">
-        <v>0.1488249276736183</v>
+        <v>0.1441741486838178</v>
       </c>
       <c r="W33">
-        <v>0.1249525006175128</v>
+        <v>0.1256352349732156</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.875440751021284</v>
+        <v>0.848083227551869</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1030892044520949</v>
+        <v>0.1040992044520949</v>
       </c>
       <c r="C34">
-        <v>28.56908793733233</v>
+        <v>26.49434210821855</v>
       </c>
       <c r="D34">
-        <v>59.65408004797327</v>
+        <v>58.63105272231703</v>
       </c>
       <c r="E34">
-        <v>27.08314176488798</v>
+        <v>28.13486026834551</v>
       </c>
       <c r="F34">
-        <v>33.65499211064095</v>
+        <v>34.70671061409848</v>
       </c>
       <c r="G34">
         <v>2.57</v>
@@ -4063,37 +4063,37 @@
         <v>4.19</v>
       </c>
       <c r="M34">
-        <v>4.940552841842091</v>
+        <v>5.094945118149657</v>
       </c>
       <c r="N34">
-        <v>-0.7505528418420919</v>
+        <v>-0.9049451181496577</v>
       </c>
       <c r="O34">
-        <v>-0.1275939831131556</v>
+        <v>-0.1538406700854418</v>
       </c>
       <c r="P34">
-        <v>-0.6229588587289363</v>
+        <v>-0.7511044480642159</v>
       </c>
       <c r="Q34">
-        <v>-0.2229588587289359</v>
+        <v>-0.3511044480642156</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09247930773627341</v>
+        <v>0.09317601382188945</v>
       </c>
       <c r="T34">
-        <v>1.078044058574444</v>
+        <v>1.094134268403913</v>
       </c>
       <c r="U34">
         <v>0.1468</v>
       </c>
       <c r="V34">
-        <v>0.1441741486838178</v>
+        <v>0.1398052350873384</v>
       </c>
       <c r="W34">
-        <v>0.1256352349732156</v>
+        <v>0.1262765914891787</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.848083227551869</v>
+        <v>0.8223837358078729</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1040992044520949</v>
+        <v>0.1238820752460972</v>
       </c>
       <c r="C35">
-        <v>26.49434210821855</v>
+        <v>10.70024695927257</v>
       </c>
       <c r="D35">
-        <v>58.63105272231703</v>
+        <v>43.88867607682857</v>
       </c>
       <c r="E35">
-        <v>28.13486026834551</v>
+        <v>29.18657877180304</v>
       </c>
       <c r="F35">
-        <v>34.70671061409848</v>
+        <v>35.75842911755601</v>
       </c>
       <c r="G35">
         <v>2.57</v>
@@ -4145,45 +4145,45 @@
         <v>4.19</v>
       </c>
       <c r="M35">
-        <v>5.094945118149657</v>
+        <v>7.180292566805246</v>
       </c>
       <c r="N35">
-        <v>-0.9049451181496577</v>
+        <v>-2.990292566805246</v>
       </c>
       <c r="O35">
-        <v>-0.1538406700854418</v>
+        <v>-0.508349736356892</v>
       </c>
       <c r="P35">
-        <v>-0.7511044480642159</v>
+        <v>-2.481942830448355</v>
       </c>
       <c r="Q35">
-        <v>-0.3511044480642156</v>
+        <v>-2.081942830448354</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09317601382188945</v>
+        <v>0.09451939402222451</v>
       </c>
       <c r="T35">
-        <v>1.094134268403913</v>
+        <v>1.125159215293869</v>
       </c>
       <c r="U35">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V35">
-        <v>0.1398052350873384</v>
+        <v>0.09920208590009115</v>
       </c>
       <c r="W35">
-        <v>0.1262765914891787</v>
+        <v>0.1808802211512617</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y35">
-        <v>0.8223837358078729</v>
+        <v>0.583541681765242</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1238820752460972</v>
+        <v>0.1254320752460972</v>
       </c>
       <c r="C36">
-        <v>10.70024695927257</v>
+        <v>8.800594656915742</v>
       </c>
       <c r="D36">
-        <v>43.88867607682857</v>
+        <v>43.04074227792928</v>
       </c>
       <c r="E36">
-        <v>29.18657877180304</v>
+        <v>30.23829727526058</v>
       </c>
       <c r="F36">
-        <v>35.75842911755601</v>
+        <v>36.81014762101354</v>
       </c>
       <c r="G36">
         <v>2.57</v>
@@ -4227,37 +4227,37 @@
         <v>4.19</v>
       </c>
       <c r="M36">
-        <v>7.180292566805246</v>
+        <v>7.391477642299519</v>
       </c>
       <c r="N36">
-        <v>-2.990292566805246</v>
+        <v>-3.20147764229952</v>
       </c>
       <c r="O36">
-        <v>-0.508349736356892</v>
+        <v>-0.5442511991909185</v>
       </c>
       <c r="P36">
-        <v>-2.481942830448355</v>
+        <v>-2.657226443108601</v>
       </c>
       <c r="Q36">
-        <v>-2.081942830448354</v>
+        <v>-2.257226443108601</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09451939402222451</v>
+        <v>0.09526892316102797</v>
       </c>
       <c r="T36">
-        <v>1.125159215293869</v>
+        <v>1.142469357067621</v>
       </c>
       <c r="U36">
         <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.09920208590009115</v>
+        <v>0.09636774058865996</v>
       </c>
       <c r="W36">
-        <v>0.1808802211512617</v>
+        <v>0.1814493576897971</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.583541681765242</v>
+        <v>0.5668690622862349</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1254320752460972</v>
+        <v>0.1269820752460971</v>
       </c>
       <c r="C37">
-        <v>8.800594656915742</v>
+        <v>6.933085680989521</v>
       </c>
       <c r="D37">
-        <v>43.04074227792928</v>
+        <v>42.22495180546059</v>
       </c>
       <c r="E37">
-        <v>30.23829727526058</v>
+        <v>31.29001577871811</v>
       </c>
       <c r="F37">
-        <v>36.81014762101354</v>
+        <v>37.86186612447107</v>
       </c>
       <c r="G37">
         <v>2.57</v>
@@ -4309,37 +4309,37 @@
         <v>4.19</v>
       </c>
       <c r="M37">
-        <v>7.391477642299519</v>
+        <v>7.602662717793791</v>
       </c>
       <c r="N37">
-        <v>-3.20147764229952</v>
+        <v>-3.412662717793792</v>
       </c>
       <c r="O37">
-        <v>-0.5442511991909185</v>
+        <v>-0.5801526620249446</v>
       </c>
       <c r="P37">
-        <v>-2.657226443108601</v>
+        <v>-2.832510055768847</v>
       </c>
       <c r="Q37">
-        <v>-2.257226443108601</v>
+        <v>-2.432510055768847</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09526892316102797</v>
+        <v>0.09604187508541903</v>
       </c>
       <c r="T37">
-        <v>1.142469357067621</v>
+        <v>1.160320440771802</v>
       </c>
       <c r="U37">
         <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.09636774058865996</v>
+        <v>0.09369085890564163</v>
       </c>
       <c r="W37">
-        <v>0.1814493576897971</v>
+        <v>0.1819868755317472</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.5668690622862349</v>
+        <v>0.5511226994449507</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1269820752460972</v>
+        <v>0.1285320752460972</v>
       </c>
       <c r="C38">
-        <v>6.933085680989507</v>
+        <v>5.095926304232826</v>
       </c>
       <c r="D38">
-        <v>42.22495180546057</v>
+        <v>41.43951093216142</v>
       </c>
       <c r="E38">
-        <v>31.2900157787181</v>
+        <v>32.34173428217563</v>
       </c>
       <c r="F38">
-        <v>37.86186612447106</v>
+        <v>38.91358462792859</v>
       </c>
       <c r="G38">
         <v>2.57</v>
@@ -4391,37 +4391,37 @@
         <v>4.19</v>
       </c>
       <c r="M38">
-        <v>7.60266271779379</v>
+        <v>7.813847793288062</v>
       </c>
       <c r="N38">
-        <v>-3.412662717793791</v>
+        <v>-3.623847793288062</v>
       </c>
       <c r="O38">
-        <v>-0.5801526620249444</v>
+        <v>-0.6160541248589706</v>
       </c>
       <c r="P38">
-        <v>-2.832510055768847</v>
+        <v>-3.007793668429092</v>
       </c>
       <c r="Q38">
-        <v>-2.432510055768846</v>
+        <v>-2.607793668429092</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09604187508541903</v>
+        <v>0.09683936516613996</v>
       </c>
       <c r="T38">
-        <v>1.160320440771802</v>
+        <v>1.178738225545958</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.09369085890564163</v>
+        <v>0.09115867352981348</v>
       </c>
       <c r="W38">
-        <v>0.1819868755317472</v>
+        <v>0.1824953383552135</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.5511226994449507</v>
+        <v>0.536227491351844</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1285320752460972</v>
+        <v>0.1300820752460972</v>
       </c>
       <c r="C39">
-        <v>5.095926304232826</v>
+        <v>3.287453825085144</v>
       </c>
       <c r="D39">
-        <v>41.43951093216142</v>
+        <v>40.68275695647127</v>
       </c>
       <c r="E39">
-        <v>32.34173428217563</v>
+        <v>33.39345278563316</v>
       </c>
       <c r="F39">
-        <v>38.91358462792859</v>
+        <v>39.96530313138612</v>
       </c>
       <c r="G39">
         <v>2.57</v>
@@ -4473,37 +4473,37 @@
         <v>4.19</v>
       </c>
       <c r="M39">
-        <v>7.813847793288062</v>
+        <v>8.025032868782333</v>
       </c>
       <c r="N39">
-        <v>-3.623847793288062</v>
+        <v>-3.835032868782333</v>
       </c>
       <c r="O39">
-        <v>-0.6160541248589706</v>
+        <v>-0.6519555876929967</v>
       </c>
       <c r="P39">
-        <v>-3.007793668429092</v>
+        <v>-3.183077281089337</v>
       </c>
       <c r="Q39">
-        <v>-2.607793668429092</v>
+        <v>-2.783077281089336</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09683936516613996</v>
+        <v>0.09766258073333577</v>
       </c>
       <c r="T39">
-        <v>1.178738225545958</v>
+        <v>1.197750132409602</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.09115867352981348</v>
+        <v>0.08875976106850263</v>
       </c>
       <c r="W39">
-        <v>0.1824953383552135</v>
+        <v>0.1829770399774447</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.536227491351844</v>
+        <v>0.5221162415794272</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1300820752460972</v>
+        <v>0.1316320752460972</v>
       </c>
       <c r="C40">
-        <v>3.287453825085144</v>
+        <v>1.506124818516042</v>
       </c>
       <c r="D40">
-        <v>40.68275695647127</v>
+        <v>39.9531464533597</v>
       </c>
       <c r="E40">
-        <v>33.39345278563316</v>
+        <v>34.44517128909069</v>
       </c>
       <c r="F40">
-        <v>39.96530313138612</v>
+        <v>41.01702163484366</v>
       </c>
       <c r="G40">
         <v>2.57</v>
@@ -4555,37 +4555,37 @@
         <v>4.19</v>
       </c>
       <c r="M40">
-        <v>8.025032868782333</v>
+        <v>8.236217944276607</v>
       </c>
       <c r="N40">
-        <v>-3.835032868782333</v>
+        <v>-4.046217944276608</v>
       </c>
       <c r="O40">
-        <v>-0.6519555876929967</v>
+        <v>-0.6878570505270233</v>
       </c>
       <c r="P40">
-        <v>-3.183077281089337</v>
+        <v>-3.358360893749584</v>
       </c>
       <c r="Q40">
-        <v>-2.783077281089336</v>
+        <v>-2.958360893749584</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09766258073333577</v>
+        <v>0.09851278697486586</v>
       </c>
       <c r="T40">
-        <v>1.197750132409602</v>
+        <v>1.217385380481891</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.08875976106850263</v>
+        <v>0.0864838697590538</v>
       </c>
       <c r="W40">
-        <v>0.1829770399774447</v>
+        <v>0.183434038952382</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.5221162415794272</v>
+        <v>0.508728645641493</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1316320752460972</v>
+        <v>0.1473486735984032</v>
       </c>
       <c r="C41">
-        <v>1.506124818516042</v>
+        <v>-5.693072908876161</v>
       </c>
       <c r="D41">
-        <v>39.9531464533597</v>
+        <v>33.80566722942503</v>
       </c>
       <c r="E41">
-        <v>34.44517128909069</v>
+        <v>35.49688979254822</v>
       </c>
       <c r="F41">
-        <v>41.01702163484366</v>
+        <v>42.06874013830119</v>
       </c>
       <c r="G41">
         <v>2.57</v>
@@ -4637,45 +4637,45 @@
         <v>4.19</v>
       </c>
       <c r="M41">
-        <v>8.236217944276607</v>
+        <v>9.91980892461142</v>
       </c>
       <c r="N41">
-        <v>-4.046217944276608</v>
+        <v>-5.729808924611421</v>
       </c>
       <c r="O41">
-        <v>-0.6878570505270233</v>
+        <v>-0.9740675171839416</v>
       </c>
       <c r="P41">
-        <v>-3.358360893749584</v>
+        <v>-4.755741407427479</v>
       </c>
       <c r="Q41">
-        <v>-2.958360893749584</v>
+        <v>-4.355741407427479</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09851278697486586</v>
+        <v>0.09966899734495707</v>
       </c>
       <c r="T41">
-        <v>1.217385380481891</v>
+        <v>1.244087698497854</v>
       </c>
       <c r="U41">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.0864838697590538</v>
+        <v>0.0718058185811177</v>
       </c>
       <c r="W41">
-        <v>0.183434038952382</v>
+        <v>0.2188681879785725</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y41">
-        <v>0.508728645641493</v>
+        <v>0.4223871681242217</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1473486735984032</v>
+        <v>0.1492486735984032</v>
       </c>
       <c r="C42">
-        <v>-5.693072908876161</v>
+        <v>-7.362134307515731</v>
       </c>
       <c r="D42">
-        <v>33.80566722942503</v>
+        <v>33.18832433424299</v>
       </c>
       <c r="E42">
-        <v>35.49688979254822</v>
+        <v>36.54860829600575</v>
       </c>
       <c r="F42">
-        <v>42.06874013830119</v>
+        <v>43.12045864175872</v>
       </c>
       <c r="G42">
         <v>2.57</v>
@@ -4719,37 +4719,37 @@
         <v>4.19</v>
       </c>
       <c r="M42">
-        <v>9.91980892461142</v>
+        <v>10.16780414772671</v>
       </c>
       <c r="N42">
-        <v>-5.729808924611421</v>
+        <v>-5.977804147726706</v>
       </c>
       <c r="O42">
-        <v>-0.9740675171839416</v>
+        <v>-1.01622670511354</v>
       </c>
       <c r="P42">
-        <v>-4.755741407427479</v>
+        <v>-4.961577442613166</v>
       </c>
       <c r="Q42">
-        <v>-4.355741407427479</v>
+        <v>-4.561577442613165</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09966899734495707</v>
+        <v>0.1005820311982614</v>
       </c>
       <c r="T42">
-        <v>1.244087698497854</v>
+        <v>1.265173930675783</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.0718058185811177</v>
+        <v>0.07005445715230996</v>
       </c>
       <c r="W42">
-        <v>0.2188681879785725</v>
+        <v>0.2192811590034853</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.4223871681242217</v>
+        <v>0.4120850420724115</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1492486735984032</v>
+        <v>0.1511486735984032</v>
       </c>
       <c r="C43">
-        <v>-7.362134307515731</v>
+        <v>-9.009052828536404</v>
       </c>
       <c r="D43">
-        <v>33.18832433424299</v>
+        <v>32.59312431667984</v>
       </c>
       <c r="E43">
-        <v>36.54860829600575</v>
+        <v>37.60032679946328</v>
       </c>
       <c r="F43">
-        <v>43.12045864175872</v>
+        <v>44.17217714521625</v>
       </c>
       <c r="G43">
         <v>2.57</v>
@@ -4801,37 +4801,37 @@
         <v>4.19</v>
       </c>
       <c r="M43">
-        <v>10.16780414772671</v>
+        <v>10.41579937084199</v>
       </c>
       <c r="N43">
-        <v>-5.977804147726706</v>
+        <v>-6.225799370841992</v>
       </c>
       <c r="O43">
-        <v>-1.01622670511354</v>
+        <v>-1.058385893043139</v>
       </c>
       <c r="P43">
-        <v>-4.961577442613166</v>
+        <v>-5.167413477798854</v>
       </c>
       <c r="Q43">
-        <v>-4.561577442613165</v>
+        <v>-4.767413477798853</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1005820311982614</v>
+        <v>0.1015265489775418</v>
       </c>
       <c r="T43">
-        <v>1.265173930675783</v>
+        <v>1.286987274308125</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.07005445715230996</v>
+        <v>0.06838649388677877</v>
       </c>
       <c r="W43">
-        <v>0.2192811590034853</v>
+        <v>0.2196744647414976</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.4120850420724115</v>
+        <v>0.4022734934516398</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1511486735984032</v>
+        <v>0.1530486735984032</v>
       </c>
       <c r="C44">
-        <v>-9.009052828536397</v>
+        <v>-10.63499881529936</v>
       </c>
       <c r="D44">
-        <v>32.59312431667984</v>
+        <v>32.01889683337441</v>
       </c>
       <c r="E44">
-        <v>37.60032679946328</v>
+        <v>38.6520453029208</v>
       </c>
       <c r="F44">
-        <v>44.17217714521624</v>
+        <v>45.22389564867377</v>
       </c>
       <c r="G44">
         <v>2.57</v>
@@ -4883,37 +4883,37 @@
         <v>4.19</v>
       </c>
       <c r="M44">
-        <v>10.41579937084199</v>
+        <v>10.66379459395728</v>
       </c>
       <c r="N44">
-        <v>-6.22579937084199</v>
+        <v>-6.473794593957276</v>
       </c>
       <c r="O44">
-        <v>-1.058385893043138</v>
+        <v>-1.100545080972737</v>
       </c>
       <c r="P44">
-        <v>-5.167413477798852</v>
+        <v>-5.373249512984539</v>
       </c>
       <c r="Q44">
-        <v>-4.767413477798851</v>
+        <v>-4.973249512984538</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1015265489775418</v>
+        <v>0.1025042077315338</v>
       </c>
       <c r="T44">
-        <v>1.286987274308124</v>
+        <v>1.309565998418793</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.06838649388677877</v>
+        <v>0.06679611030801648</v>
       </c>
       <c r="W44">
-        <v>0.2196744647414976</v>
+        <v>0.2200494771893697</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.4022734934516399</v>
+        <v>0.3929182959295087</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1530486735984032</v>
+        <v>0.1549486735984032</v>
       </c>
       <c r="C45">
-        <v>-10.63499881529936</v>
+        <v>-12.24106156238907</v>
       </c>
       <c r="D45">
-        <v>32.01889683337441</v>
+        <v>31.46455258974224</v>
       </c>
       <c r="E45">
-        <v>38.6520453029208</v>
+        <v>39.70376380637834</v>
       </c>
       <c r="F45">
-        <v>45.22389564867377</v>
+        <v>46.2756141521313</v>
       </c>
       <c r="G45">
         <v>2.57</v>
@@ -4965,37 +4965,37 @@
         <v>4.19</v>
       </c>
       <c r="M45">
-        <v>10.66379459395728</v>
+        <v>10.91178981707256</v>
       </c>
       <c r="N45">
-        <v>-6.473794593957276</v>
+        <v>-6.721789817072562</v>
       </c>
       <c r="O45">
-        <v>-1.100545080972737</v>
+        <v>-1.142704268902336</v>
       </c>
       <c r="P45">
-        <v>-5.373249512984539</v>
+        <v>-5.579085548170227</v>
       </c>
       <c r="Q45">
-        <v>-4.973249512984538</v>
+        <v>-5.179085548170226</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1025042077315338</v>
+        <v>0.1035167828695969</v>
       </c>
       <c r="T45">
-        <v>1.309565998418793</v>
+        <v>1.332951105533415</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.06679611030801648</v>
+        <v>0.06527801689192519</v>
       </c>
       <c r="W45">
-        <v>0.2200494771893697</v>
+        <v>0.2204074436168841</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3929182959295087</v>
+        <v>0.3839883346583834</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1549486735984032</v>
+        <v>0.1568486735984032</v>
       </c>
       <c r="C46">
-        <v>-12.24106156238907</v>
+        <v>-13.82825621221318</v>
       </c>
       <c r="D46">
-        <v>31.46455258974224</v>
+        <v>30.92907644337566</v>
       </c>
       <c r="E46">
-        <v>39.70376380637834</v>
+        <v>40.75548230983587</v>
       </c>
       <c r="F46">
-        <v>46.2756141521313</v>
+        <v>47.32733265558883</v>
       </c>
       <c r="G46">
         <v>2.57</v>
@@ -5047,37 +5047,37 @@
         <v>4.19</v>
       </c>
       <c r="M46">
-        <v>10.91178981707256</v>
+        <v>11.15978504018785</v>
       </c>
       <c r="N46">
-        <v>-6.721789817072562</v>
+        <v>-6.969785040187848</v>
       </c>
       <c r="O46">
-        <v>-1.142704268902336</v>
+        <v>-1.184863456831934</v>
       </c>
       <c r="P46">
-        <v>-5.579085548170227</v>
+        <v>-5.784921583355914</v>
       </c>
       <c r="Q46">
-        <v>-5.179085548170226</v>
+        <v>-5.384921583355913</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1035167828695969</v>
+        <v>0.1045661789217713</v>
       </c>
       <c r="T46">
-        <v>1.332951105533415</v>
+        <v>1.357186580179477</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.06527801689192519</v>
+        <v>0.06382739429432685</v>
       </c>
       <c r="W46">
-        <v>0.2204074436168841</v>
+        <v>0.2207495004253977</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3839883346583834</v>
+        <v>0.3754552605548638</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1568486735984032</v>
+        <v>0.1587486735984032</v>
       </c>
       <c r="C47">
-        <v>-13.82825621221318</v>
+        <v>-15.39752995917236</v>
       </c>
       <c r="D47">
-        <v>30.92907644337566</v>
+        <v>30.41152119987401</v>
       </c>
       <c r="E47">
-        <v>40.75548230983587</v>
+        <v>41.8072008132934</v>
       </c>
       <c r="F47">
-        <v>47.32733265558883</v>
+        <v>48.37905115904636</v>
       </c>
       <c r="G47">
         <v>2.57</v>
@@ -5129,37 +5129,37 @@
         <v>4.19</v>
       </c>
       <c r="M47">
-        <v>11.15978504018785</v>
+        <v>11.40778026330313</v>
       </c>
       <c r="N47">
-        <v>-6.969785040187848</v>
+        <v>-7.217780263303133</v>
       </c>
       <c r="O47">
-        <v>-1.184863456831934</v>
+        <v>-1.227022644761533</v>
       </c>
       <c r="P47">
-        <v>-5.784921583355914</v>
+        <v>-5.9907576185416</v>
       </c>
       <c r="Q47">
-        <v>-5.384921583355913</v>
+        <v>-5.5907576185416</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1045661789217713</v>
+        <v>0.1056544414943967</v>
       </c>
       <c r="T47">
-        <v>1.357186580179477</v>
+        <v>1.382319664997615</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.06382739429432685</v>
+        <v>0.06243984224445018</v>
       </c>
       <c r="W47">
-        <v>0.2207495004253977</v>
+        <v>0.2210766851987586</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3754552605548638</v>
+        <v>0.3672931896732363</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1587486735984032</v>
+        <v>0.1606486735984032</v>
       </c>
       <c r="C48">
-        <v>-15.39752995917236</v>
+        <v>-16.94976764117276</v>
       </c>
       <c r="D48">
-        <v>30.41152119987401</v>
+        <v>29.91100202133114</v>
       </c>
       <c r="E48">
-        <v>41.8072008132934</v>
+        <v>42.85891931675093</v>
       </c>
       <c r="F48">
-        <v>48.37905115904636</v>
+        <v>49.43076966250389</v>
       </c>
       <c r="G48">
         <v>2.57</v>
@@ -5211,37 +5211,37 @@
         <v>4.19</v>
       </c>
       <c r="M48">
-        <v>11.40778026330313</v>
+        <v>11.65577548641842</v>
       </c>
       <c r="N48">
-        <v>-7.217780263303133</v>
+        <v>-7.465775486418419</v>
       </c>
       <c r="O48">
-        <v>-1.227022644761533</v>
+        <v>-1.269181832691131</v>
       </c>
       <c r="P48">
-        <v>-5.9907576185416</v>
+        <v>-6.196593653727287</v>
       </c>
       <c r="Q48">
-        <v>-5.5907576185416</v>
+        <v>-5.796593653727287</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1056544414943967</v>
+        <v>0.1067837705791967</v>
       </c>
       <c r="T48">
-        <v>1.382319664997615</v>
+        <v>1.408401168110778</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.06243984224445018</v>
+        <v>0.06111133496265337</v>
       </c>
       <c r="W48">
-        <v>0.2210766851987586</v>
+        <v>0.2213899472158063</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3672931896732363</v>
+        <v>0.3594784409567845</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1606486735984032</v>
+        <v>0.1625486735984032</v>
       </c>
       <c r="C49">
-        <v>-16.94976764117276</v>
+        <v>-18.48579678792138</v>
       </c>
       <c r="D49">
-        <v>29.91100202133114</v>
+        <v>29.42669137804004</v>
       </c>
       <c r="E49">
-        <v>42.85891931675093</v>
+        <v>43.91063782020846</v>
       </c>
       <c r="F49">
-        <v>49.43076966250389</v>
+        <v>50.48248816596142</v>
       </c>
       <c r="G49">
         <v>2.57</v>
@@ -5293,37 +5293,37 @@
         <v>4.19</v>
       </c>
       <c r="M49">
-        <v>11.65577548641842</v>
+        <v>11.9037707095337</v>
       </c>
       <c r="N49">
-        <v>-7.465775486418419</v>
+        <v>-7.713770709533703</v>
       </c>
       <c r="O49">
-        <v>-1.269181832691131</v>
+        <v>-1.31134102062073</v>
       </c>
       <c r="P49">
-        <v>-6.196593653727287</v>
+        <v>-6.402429688912973</v>
       </c>
       <c r="Q49">
-        <v>-5.796593653727287</v>
+        <v>-6.002429688912973</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1067837705791967</v>
+        <v>0.1079565353980274</v>
       </c>
       <c r="T49">
-        <v>1.408401168110778</v>
+        <v>1.435485805959062</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.06111133496265337</v>
+        <v>0.05983818215093143</v>
       </c>
       <c r="W49">
-        <v>0.2213899472158063</v>
+        <v>0.2216901566488104</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3594784409567845</v>
+        <v>0.3519893067701848</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1625486735984032</v>
+        <v>0.1644486735984032</v>
       </c>
       <c r="C50">
-        <v>-18.48579678792137</v>
+        <v>-20.00639218659223</v>
       </c>
       <c r="D50">
-        <v>29.42669137804005</v>
+        <v>28.95781448282672</v>
       </c>
       <c r="E50">
-        <v>43.91063782020846</v>
+        <v>44.96235632366599</v>
       </c>
       <c r="F50">
-        <v>50.48248816596142</v>
+        <v>51.53420666941895</v>
       </c>
       <c r="G50">
         <v>2.57</v>
@@ -5375,37 +5375,37 @@
         <v>4.19</v>
       </c>
       <c r="M50">
-        <v>11.9037707095337</v>
+        <v>12.15176593264899</v>
       </c>
       <c r="N50">
-        <v>-7.713770709533703</v>
+        <v>-7.961765932648989</v>
       </c>
       <c r="O50">
-        <v>-1.31134102062073</v>
+        <v>-1.353500208550328</v>
       </c>
       <c r="P50">
-        <v>-6.402429688912973</v>
+        <v>-6.60826572409866</v>
       </c>
       <c r="Q50">
-        <v>-6.002429688912973</v>
+        <v>-6.20826572409866</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1079565353980274</v>
+        <v>0.1091752909940671</v>
       </c>
       <c r="T50">
-        <v>1.435485805959062</v>
+        <v>1.463632586468063</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.05983818215093143</v>
+        <v>0.0586169947600961</v>
       </c>
       <c r="W50">
-        <v>0.2216901566488104</v>
+        <v>0.2219781126355694</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3519893067701848</v>
+        <v>0.344805851529977</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1644486735984032</v>
+        <v>0.1663486735984032</v>
       </c>
       <c r="C51">
-        <v>-20.00639218659223</v>
+        <v>-21.51228001785006</v>
       </c>
       <c r="D51">
-        <v>28.95781448282672</v>
+        <v>28.50364515502642</v>
       </c>
       <c r="E51">
-        <v>44.96235632366599</v>
+        <v>46.01407482712352</v>
       </c>
       <c r="F51">
-        <v>51.53420666941895</v>
+        <v>52.58592517287648</v>
       </c>
       <c r="G51">
         <v>2.57</v>
@@ -5457,37 +5457,37 @@
         <v>4.19</v>
       </c>
       <c r="M51">
-        <v>12.15176593264899</v>
+        <v>12.39976115576427</v>
       </c>
       <c r="N51">
-        <v>-7.961765932648989</v>
+        <v>-8.209761155764275</v>
       </c>
       <c r="O51">
-        <v>-1.353500208550328</v>
+        <v>-1.395659396479927</v>
       </c>
       <c r="P51">
-        <v>-6.60826572409866</v>
+        <v>-6.814101759284348</v>
       </c>
       <c r="Q51">
-        <v>-6.20826572409866</v>
+        <v>-6.414101759284348</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1091752909940671</v>
+        <v>0.1104427968139485</v>
       </c>
       <c r="T51">
-        <v>1.463632586468063</v>
+        <v>1.492905238197424</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.0586169947600961</v>
+        <v>0.05744465486489417</v>
       </c>
       <c r="W51">
-        <v>0.2219781126355694</v>
+        <v>0.222254550382858</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.344805851529977</v>
+        <v>0.3379097344993774</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1663486735984032</v>
+        <v>0.1682486735984032</v>
       </c>
       <c r="C52">
-        <v>-21.51228001785006</v>
+        <v>-23.00414160867185</v>
       </c>
       <c r="D52">
-        <v>28.50364515502642</v>
+        <v>28.06350206766215</v>
       </c>
       <c r="E52">
-        <v>46.01407482712352</v>
+        <v>47.06579333058104</v>
       </c>
       <c r="F52">
-        <v>52.58592517287648</v>
+        <v>53.63764367633401</v>
       </c>
       <c r="G52">
         <v>2.57</v>
@@ -5539,37 +5539,37 @@
         <v>4.19</v>
       </c>
       <c r="M52">
-        <v>12.39976115576427</v>
+        <v>12.64775637887956</v>
       </c>
       <c r="N52">
-        <v>-8.209761155764275</v>
+        <v>-8.45775637887956</v>
       </c>
       <c r="O52">
-        <v>-1.395659396479927</v>
+        <v>-1.437818584409525</v>
       </c>
       <c r="P52">
-        <v>-6.814101759284348</v>
+        <v>-7.019937794470035</v>
       </c>
       <c r="Q52">
-        <v>-6.414101759284348</v>
+        <v>-6.619937794470035</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1104427968139485</v>
+        <v>0.1117620375652535</v>
       </c>
       <c r="T52">
-        <v>1.492905238197424</v>
+        <v>1.523372692038188</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.05744465486489417</v>
+        <v>0.05631828908322958</v>
       </c>
       <c r="W52">
-        <v>0.222254550382858</v>
+        <v>0.2225201474341745</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3379097344993774</v>
+        <v>0.3312840534307622</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1682486735984032</v>
+        <v>0.1701486735984032</v>
       </c>
       <c r="C53">
-        <v>-23.00414160867185</v>
+        <v>-24.48261684275744</v>
       </c>
       <c r="D53">
-        <v>28.06350206766215</v>
+        <v>27.63674533703409</v>
       </c>
       <c r="E53">
-        <v>47.06579333058104</v>
+        <v>48.11751183403857</v>
       </c>
       <c r="F53">
-        <v>53.63764367633401</v>
+        <v>54.68936217979154</v>
       </c>
       <c r="G53">
         <v>2.57</v>
@@ -5621,37 +5621,37 @@
         <v>4.19</v>
       </c>
       <c r="M53">
-        <v>12.64775637887956</v>
+        <v>12.89575160199485</v>
       </c>
       <c r="N53">
-        <v>-8.45775637887956</v>
+        <v>-8.705751601994846</v>
       </c>
       <c r="O53">
-        <v>-1.437818584409525</v>
+        <v>-1.479977772339124</v>
       </c>
       <c r="P53">
-        <v>-7.019937794470035</v>
+        <v>-7.225773829655722</v>
       </c>
       <c r="Q53">
-        <v>-6.619937794470035</v>
+        <v>-6.825773829655722</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1117620375652535</v>
+        <v>0.1131362466811963</v>
       </c>
       <c r="T53">
-        <v>1.523372692038188</v>
+        <v>1.555109623122317</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.05631828908322958</v>
+        <v>0.05523524506239824</v>
       </c>
       <c r="W53">
-        <v>0.2225201474341745</v>
+        <v>0.2227755292142865</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3312840534307622</v>
+        <v>0.3249132062494013</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1701486735984032</v>
+        <v>0.1720486735984032</v>
       </c>
       <c r="C54">
-        <v>-24.48261684275744</v>
+        <v>-25.94830726443221</v>
       </c>
       <c r="D54">
-        <v>27.63674533703409</v>
+        <v>27.22277341881687</v>
       </c>
       <c r="E54">
-        <v>48.11751183403857</v>
+        <v>49.16923033749611</v>
       </c>
       <c r="F54">
-        <v>54.68936217979154</v>
+        <v>55.74108068324907</v>
       </c>
       <c r="G54">
         <v>2.57</v>
@@ -5703,37 +5703,37 @@
         <v>4.19</v>
       </c>
       <c r="M54">
-        <v>12.89575160199485</v>
+        <v>13.14374682511013</v>
       </c>
       <c r="N54">
-        <v>-8.705751601994846</v>
+        <v>-8.953746825110132</v>
       </c>
       <c r="O54">
-        <v>-1.479977772339124</v>
+        <v>-1.522136960268722</v>
       </c>
       <c r="P54">
-        <v>-7.225773829655722</v>
+        <v>-7.431609864841409</v>
       </c>
       <c r="Q54">
-        <v>-6.825773829655722</v>
+        <v>-7.031609864841409</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1131362466811963</v>
+        <v>0.1145689327807962</v>
       </c>
       <c r="T54">
-        <v>1.555109623122317</v>
+        <v>1.588197061912154</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.05523524506239824</v>
+        <v>0.05419307062725864</v>
       </c>
       <c r="W54">
-        <v>0.2227755292142865</v>
+        <v>0.2230212739460924</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3249132062494013</v>
+        <v>0.3187827683956391</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1720486735984032</v>
+        <v>0.1739486735984032</v>
       </c>
       <c r="C55">
-        <v>-25.94830726443221</v>
+        <v>-27.40177890770547</v>
       </c>
       <c r="D55">
-        <v>27.22277341881687</v>
+        <v>26.82102027900113</v>
       </c>
       <c r="E55">
-        <v>49.16923033749611</v>
+        <v>50.22094884095364</v>
       </c>
       <c r="F55">
-        <v>55.74108068324907</v>
+        <v>56.7927991867066</v>
       </c>
       <c r="G55">
         <v>2.57</v>
@@ -5785,37 +5785,37 @@
         <v>4.19</v>
       </c>
       <c r="M55">
-        <v>13.14374682511013</v>
+        <v>13.39174204822542</v>
       </c>
       <c r="N55">
-        <v>-8.953746825110132</v>
+        <v>-9.201742048225418</v>
       </c>
       <c r="O55">
-        <v>-1.522136960268722</v>
+        <v>-1.564296148198321</v>
       </c>
       <c r="P55">
-        <v>-7.431609864841409</v>
+        <v>-7.637445900027097</v>
       </c>
       <c r="Q55">
-        <v>-7.031609864841409</v>
+        <v>-7.237445900027097</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1145689327807962</v>
+        <v>0.1160639095803788</v>
       </c>
       <c r="T55">
-        <v>1.588197061912154</v>
+        <v>1.622723084997201</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.05419307062725864</v>
+        <v>0.05318949524527238</v>
       </c>
       <c r="W55">
-        <v>0.2230212739460924</v>
+        <v>0.2232579170211648</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3187827683956391</v>
+        <v>0.3128793837957198</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1739486735984032</v>
+        <v>0.1758486735984032</v>
       </c>
       <c r="C56">
-        <v>-27.40177890770547</v>
+        <v>-28.84356487846526</v>
       </c>
       <c r="D56">
-        <v>26.82102027900113</v>
+        <v>26.43095281169887</v>
       </c>
       <c r="E56">
-        <v>50.22094884095364</v>
+        <v>51.27266734441117</v>
       </c>
       <c r="F56">
-        <v>56.7927991867066</v>
+        <v>57.84451769016413</v>
       </c>
       <c r="G56">
         <v>2.57</v>
@@ -5867,37 +5867,37 @@
         <v>4.19</v>
       </c>
       <c r="M56">
-        <v>13.39174204822542</v>
+        <v>13.6397372713407</v>
       </c>
       <c r="N56">
-        <v>-9.201742048225418</v>
+        <v>-9.449737271340704</v>
       </c>
       <c r="O56">
-        <v>-1.564296148198321</v>
+        <v>-1.60645533612792</v>
       </c>
       <c r="P56">
-        <v>-7.637445900027097</v>
+        <v>-7.843281935212784</v>
       </c>
       <c r="Q56">
-        <v>-7.237445900027097</v>
+        <v>-7.443281935212783</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1160639095803788</v>
+        <v>0.1176253297932761</v>
       </c>
       <c r="T56">
-        <v>1.622723084997201</v>
+        <v>1.658783597997138</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.05318949524527238</v>
+        <v>0.05222241351354015</v>
       </c>
       <c r="W56">
-        <v>0.2232579170211648</v>
+        <v>0.2234859548935072</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3128793837957198</v>
+        <v>0.3071906677267068</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1758486735984032</v>
+        <v>0.1777486735984032</v>
       </c>
       <c r="C57">
-        <v>-28.84356487846526</v>
+        <v>-30.27416771458037</v>
       </c>
       <c r="D57">
-        <v>26.43095281169887</v>
+        <v>26.05206847904129</v>
       </c>
       <c r="E57">
-        <v>51.27266734441117</v>
+        <v>52.3243858478687</v>
       </c>
       <c r="F57">
-        <v>57.84451769016413</v>
+        <v>58.89623619362166</v>
       </c>
       <c r="G57">
         <v>2.57</v>
@@ -5949,37 +5949,37 @@
         <v>4.19</v>
       </c>
       <c r="M57">
-        <v>13.6397372713407</v>
+        <v>13.88773249445599</v>
       </c>
       <c r="N57">
-        <v>-9.449737271340704</v>
+        <v>-9.697732494455989</v>
       </c>
       <c r="O57">
-        <v>-1.60645533612792</v>
+        <v>-1.648614524057518</v>
       </c>
       <c r="P57">
-        <v>-7.843281935212784</v>
+        <v>-8.049117970398472</v>
       </c>
       <c r="Q57">
-        <v>-7.443281935212783</v>
+        <v>-7.649117970398471</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1176253297932761</v>
+        <v>0.1192577236522142</v>
       </c>
       <c r="T57">
-        <v>1.658783597997138</v>
+        <v>1.696483225224346</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.05222241351354015</v>
+        <v>0.05128987041508408</v>
       </c>
       <c r="W57">
-        <v>0.2234859548935072</v>
+        <v>0.2237058485561232</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3071906677267068</v>
+        <v>0.3017051200887299</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1777486735984032</v>
+        <v>0.1796486735984032</v>
       </c>
       <c r="C58">
-        <v>-30.27416771458037</v>
+        <v>-31.69406154588053</v>
       </c>
       <c r="D58">
-        <v>26.05206847904129</v>
+        <v>25.68389315119866</v>
       </c>
       <c r="E58">
-        <v>52.3243858478687</v>
+        <v>53.37610435132623</v>
       </c>
       <c r="F58">
-        <v>58.89623619362166</v>
+        <v>59.94795469707919</v>
       </c>
       <c r="G58">
         <v>2.57</v>
@@ -6031,37 +6031,37 @@
         <v>4.19</v>
       </c>
       <c r="M58">
-        <v>13.88773249445599</v>
+        <v>14.13572771757127</v>
       </c>
       <c r="N58">
-        <v>-9.697732494455989</v>
+        <v>-9.945727717571273</v>
       </c>
       <c r="O58">
-        <v>-1.648614524057518</v>
+        <v>-1.690773711987117</v>
       </c>
       <c r="P58">
-        <v>-8.049117970398472</v>
+        <v>-8.254954005584157</v>
       </c>
       <c r="Q58">
-        <v>-7.649117970398471</v>
+        <v>-7.854954005584156</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1192577236522142</v>
+        <v>0.1209660428069168</v>
       </c>
       <c r="T58">
-        <v>1.696483225224346</v>
+        <v>1.735936323485377</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.05128987041508408</v>
+        <v>0.05039004812710015</v>
       </c>
       <c r="W58">
-        <v>0.2237058485561232</v>
+        <v>0.2239180266516298</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3017051200887299</v>
+        <v>0.2964120478064715</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1796486735984032</v>
+        <v>0.1815486735984032</v>
       </c>
       <c r="C59">
-        <v>-31.69406154588053</v>
+        <v>-33.10369407353622</v>
       </c>
       <c r="D59">
-        <v>25.68389315119866</v>
+        <v>25.3259791270005</v>
       </c>
       <c r="E59">
-        <v>53.37610435132623</v>
+        <v>54.42782285478376</v>
       </c>
       <c r="F59">
-        <v>59.94795469707919</v>
+        <v>60.99967320053673</v>
       </c>
       <c r="G59">
         <v>2.57</v>
@@ -6113,37 +6113,37 @@
         <v>4.19</v>
       </c>
       <c r="M59">
-        <v>14.13572771757127</v>
+        <v>14.38372294068656</v>
       </c>
       <c r="N59">
-        <v>-9.945727717571273</v>
+        <v>-10.19372294068656</v>
       </c>
       <c r="O59">
-        <v>-1.690773711987117</v>
+        <v>-1.732932899916716</v>
       </c>
       <c r="P59">
-        <v>-8.254954005584157</v>
+        <v>-8.460790040769846</v>
       </c>
       <c r="Q59">
-        <v>-7.854954005584156</v>
+        <v>-8.060790040769845</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1209660428069168</v>
+        <v>0.1227557104927958</v>
       </c>
       <c r="T59">
-        <v>1.735936323485377</v>
+        <v>1.77726814071122</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.05039004812710015</v>
+        <v>0.04952125419387428</v>
       </c>
       <c r="W59">
-        <v>0.2239180266516298</v>
+        <v>0.2241228882610845</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2964120478064715</v>
+        <v>0.2913014952580839</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1815486735984032</v>
+        <v>0.1834486735984032</v>
       </c>
       <c r="C60">
-        <v>-33.1036940735362</v>
+        <v>-34.50348838621279</v>
       </c>
       <c r="D60">
-        <v>25.3259791270005</v>
+        <v>24.97790331778145</v>
       </c>
       <c r="E60">
-        <v>54.42782285478375</v>
+        <v>55.47954135824128</v>
       </c>
       <c r="F60">
-        <v>60.99967320053671</v>
+        <v>62.05139170399424</v>
       </c>
       <c r="G60">
         <v>2.57</v>
@@ -6195,37 +6195,37 @@
         <v>4.19</v>
       </c>
       <c r="M60">
-        <v>14.38372294068656</v>
+        <v>14.63171816380184</v>
       </c>
       <c r="N60">
-        <v>-10.19372294068656</v>
+        <v>-10.44171816380184</v>
       </c>
       <c r="O60">
-        <v>-1.732932899916715</v>
+        <v>-1.775092087846313</v>
       </c>
       <c r="P60">
-        <v>-8.460790040769842</v>
+        <v>-8.666626075955529</v>
       </c>
       <c r="Q60">
-        <v>-8.060790040769842</v>
+        <v>-8.266626075955529</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1227557104927958</v>
+        <v>0.1246326790414006</v>
       </c>
       <c r="T60">
-        <v>1.777268140711219</v>
+        <v>1.8206161441432</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.04952125419387429</v>
+        <v>0.0486819109024527</v>
       </c>
       <c r="W60">
-        <v>0.2241228882610845</v>
+        <v>0.2243208054092017</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.291301495258084</v>
+        <v>0.2863641817791335</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1834486735984032</v>
+        <v>0.1853486735984032</v>
       </c>
       <c r="C61">
-        <v>-34.50348838621279</v>
+        <v>-35.89384462848994</v>
       </c>
       <c r="D61">
-        <v>24.97790331778145</v>
+        <v>24.63926557896182</v>
       </c>
       <c r="E61">
-        <v>55.47954135824128</v>
+        <v>56.53125986169881</v>
       </c>
       <c r="F61">
-        <v>62.05139170399424</v>
+        <v>63.10311020745177</v>
       </c>
       <c r="G61">
         <v>2.57</v>
@@ -6277,37 +6277,37 @@
         <v>4.19</v>
       </c>
       <c r="M61">
-        <v>14.63171816380184</v>
+        <v>14.87971338691713</v>
       </c>
       <c r="N61">
-        <v>-10.44171816380184</v>
+        <v>-10.68971338691713</v>
       </c>
       <c r="O61">
-        <v>-1.775092087846313</v>
+        <v>-1.817251275775912</v>
       </c>
       <c r="P61">
-        <v>-8.666626075955529</v>
+        <v>-8.872462111141218</v>
       </c>
       <c r="Q61">
-        <v>-8.266626075955529</v>
+        <v>-8.472462111141217</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1246326790414006</v>
+        <v>0.1266034960174356</v>
       </c>
       <c r="T61">
-        <v>1.8206161441432</v>
+        <v>1.86613154774678</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.0486819109024527</v>
+        <v>0.04787054572074514</v>
       </c>
       <c r="W61">
-        <v>0.2243208054092017</v>
+        <v>0.2245121253190483</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2863641817791335</v>
+        <v>0.2815914454161479</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1853486735984032</v>
+        <v>0.1872486735984032</v>
       </c>
       <c r="C62">
-        <v>-35.89384462848994</v>
+        <v>-37.2751415353787</v>
       </c>
       <c r="D62">
-        <v>24.63926557896182</v>
+        <v>24.3096871755306</v>
       </c>
       <c r="E62">
-        <v>56.53125986169881</v>
+        <v>57.58297836515634</v>
       </c>
       <c r="F62">
-        <v>63.10311020745177</v>
+        <v>64.1548287109093</v>
       </c>
       <c r="G62">
         <v>2.57</v>
@@ -6359,37 +6359,37 @@
         <v>4.19</v>
       </c>
       <c r="M62">
-        <v>14.87971338691713</v>
+        <v>15.12770861003241</v>
       </c>
       <c r="N62">
-        <v>-10.68971338691713</v>
+        <v>-10.93770861003241</v>
       </c>
       <c r="O62">
-        <v>-1.817251275775912</v>
+        <v>-1.859410463705511</v>
       </c>
       <c r="P62">
-        <v>-8.872462111141218</v>
+        <v>-9.078298146326905</v>
       </c>
       <c r="Q62">
-        <v>-8.472462111141217</v>
+        <v>-8.678298146326904</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1266034960174356</v>
+        <v>0.1286753805307032</v>
       </c>
       <c r="T62">
-        <v>1.86613154774678</v>
+        <v>1.913981074612083</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.04787054572074514</v>
+        <v>0.04708578267614277</v>
       </c>
       <c r="W62">
-        <v>0.2245121253190483</v>
+        <v>0.2246971724449656</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2815914454161479</v>
+        <v>0.2769751922126045</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1872486735984032</v>
+        <v>0.1891486735984032</v>
       </c>
       <c r="C63">
-        <v>-37.2751415353787</v>
+        <v>-38.64773784530873</v>
       </c>
       <c r="D63">
-        <v>24.3096871755306</v>
+        <v>23.98880936905811</v>
       </c>
       <c r="E63">
-        <v>57.58297836515634</v>
+        <v>58.63469686861387</v>
       </c>
       <c r="F63">
-        <v>64.1548287109093</v>
+        <v>65.20654721436684</v>
       </c>
       <c r="G63">
         <v>2.57</v>
@@ -6441,37 +6441,37 @@
         <v>4.19</v>
       </c>
       <c r="M63">
-        <v>15.12770861003241</v>
+        <v>15.3757038331477</v>
       </c>
       <c r="N63">
-        <v>-10.93770861003241</v>
+        <v>-11.1857038331477</v>
       </c>
       <c r="O63">
-        <v>-1.859410463705511</v>
+        <v>-1.901569651635109</v>
       </c>
       <c r="P63">
-        <v>-9.078298146326905</v>
+        <v>-9.284134181512592</v>
       </c>
       <c r="Q63">
-        <v>-8.678298146326904</v>
+        <v>-8.884134181512591</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1286753805307032</v>
+        <v>0.1308563115973006</v>
       </c>
       <c r="T63">
-        <v>1.913981074612083</v>
+        <v>1.96434899762819</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.04708578267614277</v>
+        <v>0.04632633456846304</v>
       </c>
       <c r="W63">
-        <v>0.2246971724449656</v>
+        <v>0.2248762503087564</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2769751922126045</v>
+        <v>0.2725078504027237</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1891486735984032</v>
+        <v>0.1910486735984032</v>
       </c>
       <c r="C64">
-        <v>-38.64773784530873</v>
+        <v>-40.01197360266823</v>
       </c>
       <c r="D64">
-        <v>23.98880936905811</v>
+        <v>23.67629211515612</v>
       </c>
       <c r="E64">
-        <v>58.63469686861387</v>
+        <v>59.68641537207139</v>
       </c>
       <c r="F64">
-        <v>65.20654721436684</v>
+        <v>66.25826571782436</v>
       </c>
       <c r="G64">
         <v>2.57</v>
@@ -6523,37 +6523,37 @@
         <v>4.19</v>
       </c>
       <c r="M64">
-        <v>15.3757038331477</v>
+        <v>15.62369905626298</v>
       </c>
       <c r="N64">
-        <v>-11.1857038331477</v>
+        <v>-11.43369905626298</v>
       </c>
       <c r="O64">
-        <v>-1.901569651635109</v>
+        <v>-1.943728839564707</v>
       </c>
       <c r="P64">
-        <v>-9.284134181512592</v>
+        <v>-9.489970216698277</v>
       </c>
       <c r="Q64">
-        <v>-8.884134181512591</v>
+        <v>-9.089970216698276</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1308563115973006</v>
+        <v>0.1331551308296601</v>
       </c>
       <c r="T64">
-        <v>1.96434899762819</v>
+        <v>2.017439511077601</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.04632633456846304</v>
+        <v>0.04559099592451919</v>
       </c>
       <c r="W64">
-        <v>0.2248762503087564</v>
+        <v>0.2250496431609984</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2725078504027237</v>
+        <v>0.26818232896776</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1910486735984032</v>
+        <v>0.1929486735984032</v>
       </c>
       <c r="C65">
-        <v>-40.01197360266823</v>
+        <v>-41.36817135983939</v>
       </c>
       <c r="D65">
-        <v>23.67629211515612</v>
+        <v>23.37181286144251</v>
       </c>
       <c r="E65">
-        <v>59.68641537207139</v>
+        <v>60.73813387552893</v>
       </c>
       <c r="F65">
-        <v>66.25826571782436</v>
+        <v>67.30998422128189</v>
       </c>
       <c r="G65">
         <v>2.57</v>
@@ -6605,37 +6605,37 @@
         <v>4.19</v>
       </c>
       <c r="M65">
-        <v>15.62369905626298</v>
+        <v>15.87169427937827</v>
       </c>
       <c r="N65">
-        <v>-11.43369905626298</v>
+        <v>-11.68169427937827</v>
       </c>
       <c r="O65">
-        <v>-1.943728839564707</v>
+        <v>-1.985888027494306</v>
       </c>
       <c r="P65">
-        <v>-9.489970216698277</v>
+        <v>-9.695806251883965</v>
       </c>
       <c r="Q65">
-        <v>-9.089970216698276</v>
+        <v>-9.295806251883965</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1331551308296601</v>
+        <v>0.1355816622415951</v>
       </c>
       <c r="T65">
-        <v>2.017439511077601</v>
+        <v>2.073479497496423</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.04559099592451919</v>
+        <v>0.04487863661319857</v>
       </c>
       <c r="W65">
-        <v>0.2250496431609984</v>
+        <v>0.2252176174866078</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.26818232896776</v>
+        <v>0.2639919800776386</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1929486735984032</v>
+        <v>0.1948486735984032</v>
       </c>
       <c r="C66">
-        <v>-41.36817135983939</v>
+        <v>-42.71663728766144</v>
       </c>
       <c r="D66">
-        <v>23.37181286144251</v>
+        <v>23.07506543707799</v>
       </c>
       <c r="E66">
-        <v>60.73813387552893</v>
+        <v>61.78985237898647</v>
       </c>
       <c r="F66">
-        <v>67.30998422128189</v>
+        <v>68.36170272473943</v>
       </c>
       <c r="G66">
         <v>2.57</v>
@@ -6687,37 +6687,37 @@
         <v>4.19</v>
       </c>
       <c r="M66">
-        <v>15.87169427937827</v>
+        <v>16.11968950249356</v>
       </c>
       <c r="N66">
-        <v>-11.68169427937827</v>
+        <v>-11.92968950249356</v>
       </c>
       <c r="O66">
-        <v>-1.985888027494306</v>
+        <v>-2.028047215423905</v>
       </c>
       <c r="P66">
-        <v>-9.695806251883965</v>
+        <v>-9.901642287069652</v>
       </c>
       <c r="Q66">
-        <v>-9.295806251883965</v>
+        <v>-9.501642287069652</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1355816622415951</v>
+        <v>0.138146852591355</v>
       </c>
       <c r="T66">
-        <v>2.073479497496423</v>
+        <v>2.132721768853463</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.04487863661319857</v>
+        <v>0.04418819604991859</v>
       </c>
       <c r="W66">
-        <v>0.2252176174866078</v>
+        <v>0.2253804233714292</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2639919800776386</v>
+        <v>0.2599305649995211</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1948486735984032</v>
+        <v>0.1967486735984032</v>
       </c>
       <c r="C67">
-        <v>-42.71663728766144</v>
+        <v>-44.05766220235859</v>
       </c>
       <c r="D67">
-        <v>23.07506543707799</v>
+        <v>22.78575902583836</v>
       </c>
       <c r="E67">
-        <v>61.78985237898647</v>
+        <v>62.84157088244399</v>
       </c>
       <c r="F67">
-        <v>68.36170272473943</v>
+        <v>69.41342122819695</v>
       </c>
       <c r="G67">
         <v>2.57</v>
@@ -6769,37 +6769,37 @@
         <v>4.19</v>
       </c>
       <c r="M67">
-        <v>16.11968950249356</v>
+        <v>16.36768472560884</v>
       </c>
       <c r="N67">
-        <v>-11.92968950249356</v>
+        <v>-12.17768472560884</v>
       </c>
       <c r="O67">
-        <v>-2.028047215423905</v>
+        <v>-2.070206403353504</v>
       </c>
       <c r="P67">
-        <v>-9.901642287069652</v>
+        <v>-10.10747832225534</v>
       </c>
       <c r="Q67">
-        <v>-9.501642287069652</v>
+        <v>-9.707478322255339</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.138146852591355</v>
+        <v>0.1408629364911007</v>
       </c>
       <c r="T67">
-        <v>2.132721768853463</v>
+        <v>2.195448879702095</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.04418819604991859</v>
+        <v>0.04351867792795013</v>
       </c>
       <c r="W67">
-        <v>0.2253804233714292</v>
+        <v>0.2255382957445894</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2599305649995211</v>
+        <v>0.255992223105589</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1967486735984032</v>
+        <v>0.1986486735984032</v>
       </c>
       <c r="C68">
-        <v>-44.05766220235859</v>
+        <v>-45.39152251617303</v>
       </c>
       <c r="D68">
-        <v>22.78575902583836</v>
+        <v>22.50361721548146</v>
       </c>
       <c r="E68">
-        <v>62.84157088244399</v>
+        <v>63.89328938590153</v>
       </c>
       <c r="F68">
-        <v>69.41342122819695</v>
+        <v>70.46513973165449</v>
       </c>
       <c r="G68">
         <v>2.57</v>
@@ -6851,37 +6851,37 @@
         <v>4.19</v>
       </c>
       <c r="M68">
-        <v>16.36768472560884</v>
+        <v>16.61567994872413</v>
       </c>
       <c r="N68">
-        <v>-12.17768472560884</v>
+        <v>-12.42567994872413</v>
       </c>
       <c r="O68">
-        <v>-2.070206403353504</v>
+        <v>-2.112365591283102</v>
       </c>
       <c r="P68">
-        <v>-10.10747832225534</v>
+        <v>-10.31331435744103</v>
       </c>
       <c r="Q68">
-        <v>-9.707478322255339</v>
+        <v>-9.913314357441026</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1408629364911007</v>
+        <v>0.1437436315362856</v>
       </c>
       <c r="T68">
-        <v>2.195448879702095</v>
+        <v>2.261977633632462</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.04351867792795013</v>
+        <v>0.04286914542156282</v>
       </c>
       <c r="W68">
-        <v>0.2255382957445894</v>
+        <v>0.2256914555095955</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.255992223105589</v>
+        <v>0.2521714436562518</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1986486735984032</v>
+        <v>0.2005486735984032</v>
       </c>
       <c r="C69">
-        <v>-45.39152251617303</v>
+        <v>-46.71848111823512</v>
       </c>
       <c r="D69">
-        <v>22.50361721548146</v>
+        <v>22.22837711687689</v>
       </c>
       <c r="E69">
-        <v>63.89328938590153</v>
+        <v>64.94500788935905</v>
       </c>
       <c r="F69">
-        <v>70.46513973165449</v>
+        <v>71.51685823511201</v>
       </c>
       <c r="G69">
         <v>2.57</v>
@@ -6933,37 +6933,37 @@
         <v>4.19</v>
       </c>
       <c r="M69">
-        <v>16.61567994872413</v>
+        <v>16.86367517183941</v>
       </c>
       <c r="N69">
-        <v>-12.42567994872413</v>
+        <v>-12.67367517183941</v>
       </c>
       <c r="O69">
-        <v>-2.112365591283102</v>
+        <v>-2.154524779212701</v>
       </c>
       <c r="P69">
-        <v>-10.31331435744103</v>
+        <v>-10.51915039262671</v>
       </c>
       <c r="Q69">
-        <v>-9.913314357441026</v>
+        <v>-10.11915039262671</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1437436315362856</v>
+        <v>0.1468043700217945</v>
       </c>
       <c r="T69">
-        <v>2.261977633632462</v>
+        <v>2.332664434683476</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.04286914542156282</v>
+        <v>0.04223871681242218</v>
       </c>
       <c r="W69">
-        <v>0.2256914555095955</v>
+        <v>0.2258401105756309</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2521714436562518</v>
+        <v>0.2484630400730716</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2005486735984032</v>
+        <v>0.2024486735984032</v>
       </c>
       <c r="C70">
-        <v>-46.71848111823512</v>
+        <v>-48.03878819157168</v>
       </c>
       <c r="D70">
-        <v>22.22837711687689</v>
+        <v>21.95978854699787</v>
       </c>
       <c r="E70">
-        <v>64.94500788935905</v>
+        <v>65.99672639281658</v>
       </c>
       <c r="F70">
-        <v>71.51685823511201</v>
+        <v>72.56857673856955</v>
       </c>
       <c r="G70">
         <v>2.57</v>
@@ -7015,37 +7015,37 @@
         <v>4.19</v>
       </c>
       <c r="M70">
-        <v>16.86367517183941</v>
+        <v>17.1116703949547</v>
       </c>
       <c r="N70">
-        <v>-12.67367517183941</v>
+        <v>-12.9216703949547</v>
       </c>
       <c r="O70">
-        <v>-2.154524779212701</v>
+        <v>-2.196683967142299</v>
       </c>
       <c r="P70">
-        <v>-10.51915039262671</v>
+        <v>-10.7249864278124</v>
       </c>
       <c r="Q70">
-        <v>-10.11915039262671</v>
+        <v>-10.3249864278124</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1468043700217945</v>
+        <v>0.1500625755063685</v>
       </c>
       <c r="T70">
-        <v>2.332664434683476</v>
+        <v>2.407911674511975</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.04223871681242218</v>
+        <v>0.04162656149630012</v>
       </c>
       <c r="W70">
-        <v>0.2258401105756309</v>
+        <v>0.2259844567991725</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2484630400730716</v>
+        <v>0.2448621264488242</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2024486735984032</v>
+        <v>0.2043486735984032</v>
       </c>
       <c r="C71">
-        <v>-48.03878819157168</v>
+        <v>-49.35268197158911</v>
       </c>
       <c r="D71">
-        <v>21.95978854699787</v>
+        <v>21.69761327043797</v>
       </c>
       <c r="E71">
-        <v>65.99672639281658</v>
+        <v>67.04844489627412</v>
       </c>
       <c r="F71">
-        <v>72.56857673856955</v>
+        <v>73.62029524202708</v>
       </c>
       <c r="G71">
         <v>2.57</v>
@@ -7097,37 +7097,37 @@
         <v>4.19</v>
       </c>
       <c r="M71">
-        <v>17.1116703949547</v>
+        <v>17.35966561806999</v>
       </c>
       <c r="N71">
-        <v>-12.9216703949547</v>
+        <v>-13.16966561806999</v>
       </c>
       <c r="O71">
-        <v>-2.196683967142299</v>
+        <v>-2.238843155071898</v>
       </c>
       <c r="P71">
-        <v>-10.7249864278124</v>
+        <v>-10.93082246299809</v>
       </c>
       <c r="Q71">
-        <v>-10.3249864278124</v>
+        <v>-10.53082246299809</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1500625755063685</v>
+        <v>0.1535379946899141</v>
       </c>
       <c r="T71">
-        <v>2.407911674511975</v>
+        <v>2.488175396995708</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.04162656149630012</v>
+        <v>0.04103189633206726</v>
       </c>
       <c r="W71">
-        <v>0.2259844567991725</v>
+        <v>0.2261246788448985</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2448621264488242</v>
+        <v>0.2413640960709839</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2043486735984032</v>
+        <v>0.2062486735984032</v>
       </c>
       <c r="C72">
-        <v>-49.35268197158911</v>
+        <v>-50.66038945086507</v>
       </c>
       <c r="D72">
-        <v>21.69761327043797</v>
+        <v>21.44162429461954</v>
       </c>
       <c r="E72">
-        <v>67.04844489627412</v>
+        <v>68.10016339973164</v>
       </c>
       <c r="F72">
-        <v>73.62029524202708</v>
+        <v>74.67201374548461</v>
       </c>
       <c r="G72">
         <v>2.57</v>
@@ -7179,37 +7179,37 @@
         <v>4.19</v>
       </c>
       <c r="M72">
-        <v>17.35966561806999</v>
+        <v>17.60766084118527</v>
       </c>
       <c r="N72">
-        <v>-13.16966561806999</v>
+        <v>-13.41766084118527</v>
       </c>
       <c r="O72">
-        <v>-2.238843155071898</v>
+        <v>-2.281002343001497</v>
       </c>
       <c r="P72">
-        <v>-10.93082246299809</v>
+        <v>-11.13665849818378</v>
       </c>
       <c r="Q72">
-        <v>-10.53082246299809</v>
+        <v>-10.73665849818378</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1535379946899141</v>
+        <v>0.1572530979550836</v>
       </c>
       <c r="T72">
-        <v>2.488175396995708</v>
+        <v>2.57397454861625</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.04103189633206726</v>
+        <v>0.04045398229922124</v>
       </c>
       <c r="W72">
-        <v>0.2261246788448985</v>
+        <v>0.2262609509738436</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2413640960709839</v>
+        <v>0.2379646017601249</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2062486735984032</v>
+        <v>0.2081486735984032</v>
       </c>
       <c r="C73">
-        <v>-50.66038945086505</v>
+        <v>-51.9621270346309</v>
       </c>
       <c r="D73">
-        <v>21.44162429461954</v>
+        <v>21.19160521431123</v>
       </c>
       <c r="E73">
-        <v>68.10016339973163</v>
+        <v>69.15188190318916</v>
       </c>
       <c r="F73">
-        <v>74.67201374548459</v>
+        <v>75.72373224894213</v>
       </c>
       <c r="G73">
         <v>2.57</v>
@@ -7261,37 +7261,37 @@
         <v>4.19</v>
       </c>
       <c r="M73">
-        <v>17.60766084118527</v>
+        <v>17.85565606430055</v>
       </c>
       <c r="N73">
-        <v>-13.41766084118527</v>
+        <v>-13.66565606430055</v>
       </c>
       <c r="O73">
-        <v>-2.281002343001496</v>
+        <v>-2.323161530931094</v>
       </c>
       <c r="P73">
-        <v>-11.13665849818377</v>
+        <v>-11.34249453336946</v>
       </c>
       <c r="Q73">
-        <v>-10.73665849818377</v>
+        <v>-10.94249453336946</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1572530979550835</v>
+        <v>0.1612335657391937</v>
       </c>
       <c r="T73">
-        <v>2.573974548616249</v>
+        <v>2.665902211066829</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.04045398229922125</v>
+        <v>0.03989212143395429</v>
       </c>
       <c r="W73">
-        <v>0.2262609509738436</v>
+        <v>0.2263934377658736</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.237964601760125</v>
+        <v>0.2346595378467899</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2081486735984032</v>
+        <v>0.2100486735984032</v>
       </c>
       <c r="C74">
-        <v>-51.9621270346309</v>
+        <v>-53.25810115092332</v>
       </c>
       <c r="D74">
-        <v>21.19160521431123</v>
+        <v>20.94734960147635</v>
       </c>
       <c r="E74">
-        <v>69.15188190318916</v>
+        <v>70.2036004066467</v>
       </c>
       <c r="F74">
-        <v>75.72373224894213</v>
+        <v>76.77545075239966</v>
       </c>
       <c r="G74">
         <v>2.57</v>
@@ -7343,37 +7343,37 @@
         <v>4.19</v>
       </c>
       <c r="M74">
-        <v>17.85565606430055</v>
+        <v>18.10365128741584</v>
       </c>
       <c r="N74">
-        <v>-13.66565606430055</v>
+        <v>-13.91365128741584</v>
       </c>
       <c r="O74">
-        <v>-2.323161530931094</v>
+        <v>-2.365320718860693</v>
       </c>
       <c r="P74">
-        <v>-11.34249453336946</v>
+        <v>-11.54833056855515</v>
       </c>
       <c r="Q74">
-        <v>-10.94249453336946</v>
+        <v>-11.14833056855515</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1612335657391937</v>
+        <v>0.1655088829887935</v>
       </c>
       <c r="T74">
-        <v>2.665902211066829</v>
+        <v>2.76463932999523</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.03989212143395429</v>
+        <v>0.03934565401705081</v>
       </c>
       <c r="W74">
-        <v>0.2263934377658736</v>
+        <v>0.2265222947827794</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2346595378467899</v>
+        <v>0.2314450236297105</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2100486735984032</v>
+        <v>0.2119486735984032</v>
       </c>
       <c r="C75">
-        <v>-53.25810115092332</v>
+        <v>-54.54850881902104</v>
       </c>
       <c r="D75">
-        <v>20.94734960147635</v>
+        <v>20.70866043683614</v>
       </c>
       <c r="E75">
-        <v>70.2036004066467</v>
+        <v>71.25531891010422</v>
       </c>
       <c r="F75">
-        <v>76.77545075239966</v>
+        <v>77.82716925585719</v>
       </c>
       <c r="G75">
         <v>2.57</v>
@@ -7425,37 +7425,37 @@
         <v>4.19</v>
       </c>
       <c r="M75">
-        <v>18.10365128741584</v>
+        <v>18.35164651053113</v>
       </c>
       <c r="N75">
-        <v>-13.91365128741584</v>
+        <v>-14.16164651053113</v>
       </c>
       <c r="O75">
-        <v>-2.365320718860693</v>
+        <v>-2.407479906790292</v>
       </c>
       <c r="P75">
-        <v>-11.54833056855515</v>
+        <v>-11.75416660374083</v>
       </c>
       <c r="Q75">
-        <v>-11.14833056855515</v>
+        <v>-11.35416660374083</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1655088829887935</v>
+        <v>0.1701130707960548</v>
       </c>
       <c r="T75">
-        <v>2.76463932999523</v>
+        <v>2.870971611918124</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.03934565401705081</v>
+        <v>0.03881395598979336</v>
       </c>
       <c r="W75">
-        <v>0.2265222947827794</v>
+        <v>0.2266476691776068</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2314450236297105</v>
+        <v>0.228317388175255</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2119486735984032</v>
+        <v>0.2138486735984032</v>
       </c>
       <c r="C76">
-        <v>-54.54850881902104</v>
+        <v>-55.83353817945631</v>
       </c>
       <c r="D76">
-        <v>20.70866043683614</v>
+        <v>20.47534957985841</v>
       </c>
       <c r="E76">
-        <v>71.25531891010422</v>
+        <v>72.30703741356176</v>
       </c>
       <c r="F76">
-        <v>77.82716925585719</v>
+        <v>78.87888775931472</v>
       </c>
       <c r="G76">
         <v>2.57</v>
@@ -7507,37 +7507,37 @@
         <v>4.19</v>
       </c>
       <c r="M76">
-        <v>18.35164651053113</v>
+        <v>18.59964173364641</v>
       </c>
       <c r="N76">
-        <v>-14.16164651053113</v>
+        <v>-14.40964173364641</v>
       </c>
       <c r="O76">
-        <v>-2.407479906790292</v>
+        <v>-2.44963909471989</v>
       </c>
       <c r="P76">
-        <v>-11.75416660374083</v>
+        <v>-11.96000263892652</v>
       </c>
       <c r="Q76">
-        <v>-11.35416660374083</v>
+        <v>-11.56000263892652</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1701130707960548</v>
+        <v>0.1750855936278969</v>
       </c>
       <c r="T76">
-        <v>2.870971611918124</v>
+        <v>2.985810476394849</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.03881395598979336</v>
+        <v>0.03829643657659611</v>
       </c>
       <c r="W76">
-        <v>0.2266476691776068</v>
+        <v>0.2267697002552387</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.228317388175255</v>
+        <v>0.2252731563329183</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2138486735984032</v>
+        <v>0.2157486735984032</v>
       </c>
       <c r="C77">
-        <v>-55.83353817945631</v>
+        <v>-57.11336898859761</v>
       </c>
       <c r="D77">
-        <v>20.47534957985841</v>
+        <v>20.24723727417463</v>
       </c>
       <c r="E77">
-        <v>72.30703741356176</v>
+        <v>73.35875591701928</v>
       </c>
       <c r="F77">
-        <v>78.87888775931472</v>
+        <v>79.93060626277224</v>
       </c>
       <c r="G77">
         <v>2.57</v>
@@ -7589,37 +7589,37 @@
         <v>4.19</v>
       </c>
       <c r="M77">
-        <v>18.59964173364641</v>
+        <v>18.8476369567617</v>
       </c>
       <c r="N77">
-        <v>-14.40964173364641</v>
+        <v>-14.6576369567617</v>
       </c>
       <c r="O77">
-        <v>-2.44963909471989</v>
+        <v>-2.491798282649489</v>
       </c>
       <c r="P77">
-        <v>-11.96000263892652</v>
+        <v>-12.16583867411221</v>
       </c>
       <c r="Q77">
-        <v>-11.56000263892652</v>
+        <v>-11.76583867411221</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1750855936278969</v>
+        <v>0.1804724933623927</v>
       </c>
       <c r="T77">
-        <v>2.985810476394849</v>
+        <v>3.110219246244634</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03829643657659611</v>
+        <v>0.03779253609532511</v>
       </c>
       <c r="W77">
-        <v>0.2267697002552387</v>
+        <v>0.2268885199887224</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2252731563329183</v>
+        <v>0.2223090358548536</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2157486735984032</v>
+        <v>0.2176486735984032</v>
       </c>
       <c r="C78">
-        <v>-57.11336898859761</v>
+        <v>-58.38817308053655</v>
       </c>
       <c r="D78">
-        <v>20.24723727417463</v>
+        <v>20.02415168569323</v>
       </c>
       <c r="E78">
-        <v>73.35875591701928</v>
+        <v>74.41047442047682</v>
       </c>
       <c r="F78">
-        <v>79.93060626277224</v>
+        <v>80.98232476622978</v>
       </c>
       <c r="G78">
         <v>2.57</v>
@@ -7671,37 +7671,37 @@
         <v>4.19</v>
       </c>
       <c r="M78">
-        <v>18.8476369567617</v>
+        <v>19.09563217987698</v>
       </c>
       <c r="N78">
-        <v>-14.6576369567617</v>
+        <v>-14.90563217987698</v>
       </c>
       <c r="O78">
-        <v>-2.491798282649489</v>
+        <v>-2.533957470579087</v>
       </c>
       <c r="P78">
-        <v>-12.16583867411221</v>
+        <v>-12.3716747092979</v>
       </c>
       <c r="Q78">
-        <v>-11.76583867411221</v>
+        <v>-11.9716747092979</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1804724933623927</v>
+        <v>0.1863278191607576</v>
       </c>
       <c r="T78">
-        <v>3.110219246244634</v>
+        <v>3.245446169994401</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.03779253609532511</v>
+        <v>0.03730172393824296</v>
       </c>
       <c r="W78">
-        <v>0.2268885199887224</v>
+        <v>0.2270042534953623</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2223090358548536</v>
+        <v>0.2194219055190763</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2176486735984032</v>
+        <v>0.2195486735984032</v>
       </c>
       <c r="C79">
-        <v>-58.38817308053655</v>
+        <v>-59.65811479877264</v>
       </c>
       <c r="D79">
-        <v>20.02415168569323</v>
+        <v>19.80592847091468</v>
       </c>
       <c r="E79">
-        <v>74.41047442047682</v>
+        <v>75.46219292393435</v>
       </c>
       <c r="F79">
-        <v>80.98232476622978</v>
+        <v>82.03404326968732</v>
       </c>
       <c r="G79">
         <v>2.57</v>
@@ -7753,37 +7753,37 @@
         <v>4.19</v>
       </c>
       <c r="M79">
-        <v>19.09563217987698</v>
+        <v>19.34362740299227</v>
       </c>
       <c r="N79">
-        <v>-14.90563217987698</v>
+        <v>-15.15362740299227</v>
       </c>
       <c r="O79">
-        <v>-2.533957470579087</v>
+        <v>-2.576116658508686</v>
       </c>
       <c r="P79">
-        <v>-12.3716747092979</v>
+        <v>-12.57751074448358</v>
       </c>
       <c r="Q79">
-        <v>-11.9716747092979</v>
+        <v>-12.17751074448358</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1863278191607576</v>
+        <v>0.1927154473044284</v>
       </c>
       <c r="T79">
-        <v>3.245446169994401</v>
+        <v>3.392966450448692</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.03730172393824296</v>
+        <v>0.03682349670826549</v>
       </c>
       <c r="W79">
-        <v>0.2270042534953623</v>
+        <v>0.227117019476191</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2194219055190763</v>
+        <v>0.2166088041662676</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2195486735984032</v>
+        <v>0.2214486735984032</v>
       </c>
       <c r="C80">
-        <v>-59.65811479877264</v>
+        <v>-60.92335139997552</v>
       </c>
       <c r="D80">
-        <v>19.80592847091468</v>
+        <v>19.59241037316932</v>
       </c>
       <c r="E80">
-        <v>75.46219292393435</v>
+        <v>76.51391142739188</v>
       </c>
       <c r="F80">
-        <v>82.03404326968732</v>
+        <v>83.08576177314484</v>
       </c>
       <c r="G80">
         <v>2.57</v>
@@ -7835,37 +7835,37 @@
         <v>4.19</v>
       </c>
       <c r="M80">
-        <v>19.34362740299227</v>
+        <v>19.59162262610755</v>
       </c>
       <c r="N80">
-        <v>-15.15362740299227</v>
+        <v>-15.40162262610755</v>
       </c>
       <c r="O80">
-        <v>-2.576116658508686</v>
+        <v>-2.618275846438284</v>
       </c>
       <c r="P80">
-        <v>-12.57751074448358</v>
+        <v>-12.78334677966927</v>
       </c>
       <c r="Q80">
-        <v>-12.17751074448358</v>
+        <v>-12.38334677966927</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1927154473044284</v>
+        <v>0.1997114209855916</v>
       </c>
       <c r="T80">
-        <v>3.392966450448692</v>
+        <v>3.554536281422439</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03682349670826549</v>
+        <v>0.03635737649676846</v>
       </c>
       <c r="W80">
-        <v>0.227117019476191</v>
+        <v>0.227226930622062</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2166088041662676</v>
+        <v>0.2138669205692262</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2214486735984032</v>
+        <v>0.2233486735984032</v>
       </c>
       <c r="C81">
-        <v>-60.92335139997552</v>
+        <v>-62.18403343190914</v>
       </c>
       <c r="D81">
-        <v>19.59241037316932</v>
+        <v>19.38344684469324</v>
       </c>
       <c r="E81">
-        <v>76.51391142739188</v>
+        <v>77.56562993084941</v>
       </c>
       <c r="F81">
-        <v>83.08576177314484</v>
+        <v>84.13748027660237</v>
       </c>
       <c r="G81">
         <v>2.57</v>
@@ -7917,37 +7917,37 @@
         <v>4.19</v>
       </c>
       <c r="M81">
-        <v>19.59162262610755</v>
+        <v>19.83961784922284</v>
       </c>
       <c r="N81">
-        <v>-15.40162262610755</v>
+        <v>-15.64961784922284</v>
       </c>
       <c r="O81">
-        <v>-2.618275846438284</v>
+        <v>-2.660435034367883</v>
       </c>
       <c r="P81">
-        <v>-12.78334677966927</v>
+        <v>-12.98918281485496</v>
       </c>
       <c r="Q81">
-        <v>-12.38334677966927</v>
+        <v>-12.58918281485496</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1997114209855916</v>
+        <v>0.2074069920348712</v>
       </c>
       <c r="T81">
-        <v>3.554536281422439</v>
+        <v>3.732263095493562</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03635737649676846</v>
+        <v>0.03590290929055885</v>
       </c>
       <c r="W81">
-        <v>0.227226930622062</v>
+        <v>0.2273340939892862</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2138669205692262</v>
+        <v>0.2111935840621109</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2233486735984032</v>
+        <v>0.2252486735984032</v>
       </c>
       <c r="C82">
-        <v>-62.18403343190914</v>
+        <v>-63.44030508742642</v>
       </c>
       <c r="D82">
-        <v>19.38344684469324</v>
+        <v>19.17889369263347</v>
       </c>
       <c r="E82">
-        <v>77.56562993084941</v>
+        <v>78.61734843430693</v>
       </c>
       <c r="F82">
-        <v>84.13748027660237</v>
+        <v>85.1891987800599</v>
       </c>
       <c r="G82">
         <v>2.57</v>
@@ -7999,37 +7999,37 @@
         <v>4.19</v>
       </c>
       <c r="M82">
-        <v>19.83961784922284</v>
+        <v>20.08761307233813</v>
       </c>
       <c r="N82">
-        <v>-15.64961784922284</v>
+        <v>-15.89761307233813</v>
       </c>
       <c r="O82">
-        <v>-2.660435034367883</v>
+        <v>-2.702594222297482</v>
       </c>
       <c r="P82">
-        <v>-12.98918281485496</v>
+        <v>-13.19501885004065</v>
       </c>
       <c r="Q82">
-        <v>-12.58918281485496</v>
+        <v>-12.79501885004064</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2074069920348712</v>
+        <v>0.2159126231946013</v>
       </c>
       <c r="T82">
-        <v>3.732263095493562</v>
+        <v>3.928697995256381</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03590290929055885</v>
+        <v>0.03545966349684825</v>
       </c>
       <c r="W82">
-        <v>0.2273340939892862</v>
+        <v>0.2274386113474432</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2111935840621109</v>
+        <v>0.2085862558638132</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2252486735984032</v>
+        <v>0.2271486735984032</v>
       </c>
       <c r="C83">
-        <v>-63.44030508742642</v>
+        <v>-64.69230453628408</v>
       </c>
       <c r="D83">
-        <v>19.17889369263347</v>
+        <v>18.97861274723335</v>
       </c>
       <c r="E83">
-        <v>78.61734843430693</v>
+        <v>79.66906693776447</v>
       </c>
       <c r="F83">
-        <v>85.1891987800599</v>
+        <v>86.24091728351743</v>
       </c>
       <c r="G83">
         <v>2.57</v>
@@ -8081,37 +8081,37 @@
         <v>4.19</v>
       </c>
       <c r="M83">
-        <v>20.08761307233813</v>
+        <v>20.33560829545341</v>
       </c>
       <c r="N83">
-        <v>-15.89761307233813</v>
+        <v>-16.14560829545341</v>
       </c>
       <c r="O83">
-        <v>-2.702594222297482</v>
+        <v>-2.744753410227081</v>
       </c>
       <c r="P83">
-        <v>-13.19501885004065</v>
+        <v>-13.40085488522633</v>
       </c>
       <c r="Q83">
-        <v>-12.79501885004064</v>
+        <v>-13.00085488522633</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2159126231946013</v>
+        <v>0.2253633244831903</v>
       </c>
       <c r="T83">
-        <v>3.928697995256381</v>
+        <v>4.146958994992847</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03545966349684825</v>
+        <v>0.03502722857615498</v>
       </c>
       <c r="W83">
-        <v>0.2274386113474432</v>
+        <v>0.2275405795017426</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2085862558638132</v>
+        <v>0.2060425210362057</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2271486735984032</v>
+        <v>0.2290486735984033</v>
       </c>
       <c r="C84">
-        <v>-64.69230453628408</v>
+        <v>-65.94016423638161</v>
       </c>
       <c r="D84">
-        <v>18.97861274723335</v>
+        <v>18.78247155059337</v>
       </c>
       <c r="E84">
-        <v>79.66906693776447</v>
+        <v>80.72078544122201</v>
       </c>
       <c r="F84">
-        <v>86.24091728351743</v>
+        <v>87.29263578697497</v>
       </c>
       <c r="G84">
         <v>2.57</v>
@@ -8163,37 +8163,37 @@
         <v>4.19</v>
       </c>
       <c r="M84">
-        <v>20.33560829545341</v>
+        <v>20.5836035185687</v>
       </c>
       <c r="N84">
-        <v>-16.14560829545341</v>
+        <v>-16.3936035185687</v>
       </c>
       <c r="O84">
-        <v>-2.744753410227081</v>
+        <v>-2.786912598156678</v>
       </c>
       <c r="P84">
-        <v>-13.40085488522633</v>
+        <v>-13.60669092041202</v>
       </c>
       <c r="Q84">
-        <v>-13.00085488522633</v>
+        <v>-13.20669092041202</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2253633244831903</v>
+        <v>0.2359258729822015</v>
       </c>
       <c r="T84">
-        <v>4.146958994992847</v>
+        <v>4.390897759404191</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03502722857615498</v>
+        <v>0.03460521377403263</v>
       </c>
       <c r="W84">
-        <v>0.2275405795017426</v>
+        <v>0.2276400905920831</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2060425210362057</v>
+        <v>0.2035600810237214</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2290486735984033</v>
+        <v>0.2309486735984032</v>
       </c>
       <c r="C85">
-        <v>-65.94016423638161</v>
+        <v>-67.18401122589809</v>
       </c>
       <c r="D85">
-        <v>18.78247155059337</v>
+        <v>18.5903430645344</v>
       </c>
       <c r="E85">
-        <v>80.72078544122201</v>
+        <v>81.77250394467953</v>
       </c>
       <c r="F85">
-        <v>87.29263578697497</v>
+        <v>88.34435429043249</v>
       </c>
       <c r="G85">
         <v>2.57</v>
@@ -8245,37 +8245,37 @@
         <v>4.19</v>
       </c>
       <c r="M85">
-        <v>20.5836035185687</v>
+        <v>20.83159874168398</v>
       </c>
       <c r="N85">
-        <v>-16.3936035185687</v>
+        <v>-16.64159874168399</v>
       </c>
       <c r="O85">
-        <v>-2.786912598156678</v>
+        <v>-2.829071786086278</v>
       </c>
       <c r="P85">
-        <v>-13.60669092041202</v>
+        <v>-13.81252695559771</v>
       </c>
       <c r="Q85">
-        <v>-13.20669092041202</v>
+        <v>-13.41252695559771</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2359258729822015</v>
+        <v>0.2478087400435891</v>
       </c>
       <c r="T85">
-        <v>4.390897759404191</v>
+        <v>4.665328869366954</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03460521377403263</v>
+        <v>0.03419324694338938</v>
       </c>
       <c r="W85">
-        <v>0.2276400905920831</v>
+        <v>0.2277372323707488</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2035600810237214</v>
+        <v>0.2011367467258198</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2309486735984032</v>
+        <v>0.2328486735984032</v>
       </c>
       <c r="C86">
-        <v>-67.18401122589808</v>
+        <v>-68.42396739768097</v>
       </c>
       <c r="D86">
-        <v>18.5903430645344</v>
+        <v>18.40210539620904</v>
       </c>
       <c r="E86">
-        <v>81.77250394467951</v>
+        <v>82.82422244813705</v>
       </c>
       <c r="F86">
-        <v>88.34435429043248</v>
+        <v>89.39607279389001</v>
       </c>
       <c r="G86">
         <v>2.57</v>
@@ -8327,37 +8327,37 @@
         <v>4.19</v>
       </c>
       <c r="M86">
-        <v>20.83159874168398</v>
+        <v>21.07959396479927</v>
       </c>
       <c r="N86">
-        <v>-16.64159874168398</v>
+        <v>-16.88959396479927</v>
       </c>
       <c r="O86">
-        <v>-2.829071786086276</v>
+        <v>-2.871230974015876</v>
       </c>
       <c r="P86">
-        <v>-13.8125269555977</v>
+        <v>-14.01836299078339</v>
       </c>
       <c r="Q86">
-        <v>-13.4125269555977</v>
+        <v>-13.61836299078339</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.247808740043589</v>
+        <v>0.2612759893798282</v>
       </c>
       <c r="T86">
-        <v>4.665328869366951</v>
+        <v>4.976350793991414</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03419324694338938</v>
+        <v>0.03379097344993775</v>
       </c>
       <c r="W86">
-        <v>0.2277372323707488</v>
+        <v>0.2278320884605047</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.20113674672582</v>
+        <v>0.1987704320584572</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2328486735984032</v>
+        <v>0.2347486735984032</v>
       </c>
       <c r="C87">
-        <v>-68.42396739768097</v>
+        <v>-69.66014975713153</v>
       </c>
       <c r="D87">
-        <v>18.40210539620904</v>
+        <v>18.217641540216</v>
       </c>
       <c r="E87">
-        <v>82.82422244813705</v>
+        <v>83.87594095159457</v>
       </c>
       <c r="F87">
-        <v>89.39607279389001</v>
+        <v>90.44779129734754</v>
       </c>
       <c r="G87">
         <v>2.57</v>
@@ -8409,37 +8409,37 @@
         <v>4.19</v>
       </c>
       <c r="M87">
-        <v>21.07959396479927</v>
+        <v>21.32758918791455</v>
       </c>
       <c r="N87">
-        <v>-16.88959396479927</v>
+        <v>-17.13758918791455</v>
       </c>
       <c r="O87">
-        <v>-2.871230974015876</v>
+        <v>-2.913390161945474</v>
       </c>
       <c r="P87">
-        <v>-14.01836299078339</v>
+        <v>-14.22419902596908</v>
       </c>
       <c r="Q87">
-        <v>-13.61836299078339</v>
+        <v>-13.82419902596908</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2612759893798282</v>
+        <v>0.2766671314783873</v>
       </c>
       <c r="T87">
-        <v>4.976350793991414</v>
+        <v>5.331804422133658</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03379097344993775</v>
+        <v>0.03339805515400824</v>
       </c>
       <c r="W87">
-        <v>0.2278320884605047</v>
+        <v>0.2279247385946848</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1987704320584572</v>
+        <v>0.1964591479647544</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2347486735984032</v>
+        <v>0.2366486735984032</v>
       </c>
       <c r="C88">
-        <v>-69.66014975713153</v>
+        <v>-70.89267066473415</v>
       </c>
       <c r="D88">
-        <v>18.217641540216</v>
+        <v>18.03683913607092</v>
       </c>
       <c r="E88">
-        <v>83.87594095159457</v>
+        <v>84.92765945505211</v>
       </c>
       <c r="F88">
-        <v>90.44779129734754</v>
+        <v>91.49950980080507</v>
       </c>
       <c r="G88">
         <v>2.57</v>
@@ -8491,37 +8491,37 @@
         <v>4.19</v>
       </c>
       <c r="M88">
-        <v>21.32758918791455</v>
+        <v>21.57558441102984</v>
       </c>
       <c r="N88">
-        <v>-17.13758918791455</v>
+        <v>-17.38558441102984</v>
       </c>
       <c r="O88">
-        <v>-2.913390161945474</v>
+        <v>-2.955549349875073</v>
       </c>
       <c r="P88">
-        <v>-14.22419902596908</v>
+        <v>-14.43003506115477</v>
       </c>
       <c r="Q88">
-        <v>-13.82419902596908</v>
+        <v>-14.03003506115477</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2766671314783873</v>
+        <v>0.2944261415921094</v>
       </c>
       <c r="T88">
-        <v>5.331804422133658</v>
+        <v>5.741943223836246</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03339805515400824</v>
+        <v>0.03301416946258286</v>
       </c>
       <c r="W88">
-        <v>0.2279247385946848</v>
+        <v>0.228015258840723</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1964591479647544</v>
+        <v>0.1942009968387226</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2366486735984032</v>
+        <v>0.2385486735984032</v>
       </c>
       <c r="C89">
-        <v>-70.89267066473415</v>
+        <v>-72.12163806428541</v>
       </c>
       <c r="D89">
-        <v>18.03683913607092</v>
+        <v>17.85959023997721</v>
       </c>
       <c r="E89">
-        <v>84.92765945505211</v>
+        <v>85.97937795850964</v>
       </c>
       <c r="F89">
-        <v>91.49950980080507</v>
+        <v>92.55122830426261</v>
       </c>
       <c r="G89">
         <v>2.57</v>
@@ -8573,37 +8573,37 @@
         <v>4.19</v>
       </c>
       <c r="M89">
-        <v>21.57558441102984</v>
+        <v>21.82357963414512</v>
       </c>
       <c r="N89">
-        <v>-17.38558441102984</v>
+        <v>-17.63357963414512</v>
       </c>
       <c r="O89">
-        <v>-2.955549349875073</v>
+        <v>-2.997708537804671</v>
       </c>
       <c r="P89">
-        <v>-14.43003506115477</v>
+        <v>-14.63587109634045</v>
       </c>
       <c r="Q89">
-        <v>-14.03003506115477</v>
+        <v>-14.23587109634045</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2944261415921094</v>
+        <v>0.3151449867247853</v>
       </c>
       <c r="T89">
-        <v>5.741943223836246</v>
+        <v>6.220438492489269</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03301416946258286</v>
+        <v>0.0326390084459626</v>
       </c>
       <c r="W89">
-        <v>0.228015258840723</v>
+        <v>0.228103721808442</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1942009968387226</v>
+        <v>0.1919941673291918</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2385486735984032</v>
+        <v>0.2404486735984032</v>
       </c>
       <c r="C90">
-        <v>-72.12163806428541</v>
+        <v>-73.34715569779716</v>
       </c>
       <c r="D90">
-        <v>17.85959023997721</v>
+        <v>17.68579110992296</v>
       </c>
       <c r="E90">
-        <v>85.97937795850964</v>
+        <v>87.03109646196717</v>
       </c>
       <c r="F90">
-        <v>92.55122830426261</v>
+        <v>93.60294680772013</v>
       </c>
       <c r="G90">
         <v>2.57</v>
@@ -8655,37 +8655,37 @@
         <v>4.19</v>
       </c>
       <c r="M90">
-        <v>21.82357963414512</v>
+        <v>22.07157485726041</v>
       </c>
       <c r="N90">
-        <v>-17.63357963414512</v>
+        <v>-17.88157485726041</v>
       </c>
       <c r="O90">
-        <v>-2.997708537804671</v>
+        <v>-3.03986772573427</v>
       </c>
       <c r="P90">
-        <v>-14.63587109634045</v>
+        <v>-14.84170713152614</v>
       </c>
       <c r="Q90">
-        <v>-14.23587109634045</v>
+        <v>-14.44170713152614</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3151449867247853</v>
+        <v>0.3396308946088568</v>
       </c>
       <c r="T90">
-        <v>6.220438492489269</v>
+        <v>6.785932900897385</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.0326390084459626</v>
+        <v>0.03227227801398549</v>
       </c>
       <c r="W90">
-        <v>0.228103721808442</v>
+        <v>0.2281901968443022</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1919941673291918</v>
+        <v>0.1898369294940322</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2404486735984032</v>
+        <v>0.2423486735984032</v>
       </c>
       <c r="C91">
-        <v>-73.34715569779716</v>
+        <v>-74.56932330797304</v>
       </c>
       <c r="D91">
-        <v>17.68579110992296</v>
+        <v>17.51534200320463</v>
       </c>
       <c r="E91">
-        <v>87.03109646196717</v>
+        <v>88.0828149654247</v>
       </c>
       <c r="F91">
-        <v>93.60294680772013</v>
+        <v>94.65466531117767</v>
       </c>
       <c r="G91">
         <v>2.57</v>
@@ -8737,37 +8737,37 @@
         <v>4.19</v>
       </c>
       <c r="M91">
-        <v>22.07157485726041</v>
+        <v>22.31957008037569</v>
       </c>
       <c r="N91">
-        <v>-17.88157485726041</v>
+        <v>-18.12957008037569</v>
       </c>
       <c r="O91">
-        <v>-3.03986772573427</v>
+        <v>-3.082026913663868</v>
       </c>
       <c r="P91">
-        <v>-14.84170713152614</v>
+        <v>-15.04754316671183</v>
       </c>
       <c r="Q91">
-        <v>-14.44170713152614</v>
+        <v>-14.64754316671183</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3396308946088568</v>
+        <v>0.3690139840697424</v>
       </c>
       <c r="T91">
-        <v>6.785932900897385</v>
+        <v>7.464526190987122</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03227227801398549</v>
+        <v>0.03191369714716343</v>
       </c>
       <c r="W91">
-        <v>0.2281901968443022</v>
+        <v>0.2282747502126989</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1898369294940322</v>
+        <v>0.187727630277432</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2423486735984032</v>
+        <v>0.2442486735984032</v>
       </c>
       <c r="C92">
-        <v>-74.56932330797304</v>
+        <v>-75.78823682908775</v>
       </c>
       <c r="D92">
-        <v>17.51534200320463</v>
+        <v>17.34814698554744</v>
       </c>
       <c r="E92">
-        <v>88.0828149654247</v>
+        <v>89.13453346888222</v>
       </c>
       <c r="F92">
-        <v>94.65466531117767</v>
+        <v>95.70638381463519</v>
       </c>
       <c r="G92">
         <v>2.57</v>
@@ -8819,37 +8819,37 @@
         <v>4.19</v>
       </c>
       <c r="M92">
-        <v>22.31957008037569</v>
+        <v>22.56756530349098</v>
       </c>
       <c r="N92">
-        <v>-18.12957008037569</v>
+        <v>-18.37756530349098</v>
       </c>
       <c r="O92">
-        <v>-3.082026913663868</v>
+        <v>-3.124186101593467</v>
       </c>
       <c r="P92">
-        <v>-15.04754316671183</v>
+        <v>-15.25337920189751</v>
       </c>
       <c r="Q92">
-        <v>-14.64754316671183</v>
+        <v>-14.85337920189751</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3690139840697424</v>
+        <v>0.4049266489663805</v>
       </c>
       <c r="T92">
-        <v>7.464526190987122</v>
+        <v>8.293917989985694</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03191369714716343</v>
+        <v>0.03156299717851328</v>
       </c>
       <c r="W92">
-        <v>0.2282747502126989</v>
+        <v>0.2283574452653066</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.187727630277432</v>
+        <v>0.1856646892853722</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2442486735984032</v>
+        <v>0.2461486735984032</v>
       </c>
       <c r="C93">
-        <v>-75.78823682908775</v>
+        <v>-77.00398856703795</v>
       </c>
       <c r="D93">
-        <v>17.34814698554744</v>
+        <v>17.18411375105478</v>
       </c>
       <c r="E93">
-        <v>89.13453346888222</v>
+        <v>90.18625197233976</v>
       </c>
       <c r="F93">
-        <v>95.70638381463519</v>
+        <v>96.75810231809272</v>
       </c>
       <c r="G93">
         <v>2.57</v>
@@ -8901,37 +8901,37 @@
         <v>4.19</v>
       </c>
       <c r="M93">
-        <v>22.56756530349098</v>
+        <v>22.81556052660627</v>
       </c>
       <c r="N93">
-        <v>-18.37756530349098</v>
+        <v>-18.62556052660626</v>
       </c>
       <c r="O93">
-        <v>-3.124186101593467</v>
+        <v>-3.166345289523065</v>
       </c>
       <c r="P93">
-        <v>-15.25337920189751</v>
+        <v>-15.4592152370832</v>
       </c>
       <c r="Q93">
-        <v>-14.85337920189751</v>
+        <v>-15.0592152370832</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4049266489663805</v>
+        <v>0.4498174800871782</v>
       </c>
       <c r="T93">
-        <v>8.293917989985694</v>
+        <v>9.330657738733908</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03156299717851328</v>
+        <v>0.03121992112222509</v>
       </c>
       <c r="W93">
-        <v>0.2283574452653066</v>
+        <v>0.2284383425993793</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1856646892853722</v>
+        <v>0.1836465948366183</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2461486735984032</v>
+        <v>0.2480486735984032</v>
       </c>
       <c r="C94">
-        <v>-77.00398856703795</v>
+        <v>-78.21666736927368</v>
       </c>
       <c r="D94">
-        <v>17.18411375105478</v>
+        <v>17.02315345227658</v>
       </c>
       <c r="E94">
-        <v>90.18625197233976</v>
+        <v>91.2379704757973</v>
       </c>
       <c r="F94">
-        <v>96.75810231809272</v>
+        <v>97.80982082155026</v>
       </c>
       <c r="G94">
         <v>2.57</v>
@@ -8983,37 +8983,37 @@
         <v>4.19</v>
       </c>
       <c r="M94">
-        <v>22.81556052660627</v>
+        <v>23.06355574972155</v>
       </c>
       <c r="N94">
-        <v>-18.62556052660626</v>
+        <v>-18.87355574972155</v>
       </c>
       <c r="O94">
-        <v>-3.166345289523065</v>
+        <v>-3.208504477452665</v>
       </c>
       <c r="P94">
-        <v>-15.4592152370832</v>
+        <v>-15.66505127226889</v>
       </c>
       <c r="Q94">
-        <v>-15.0592152370832</v>
+        <v>-15.26505127226889</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4498174800871782</v>
+        <v>0.5075342629567751</v>
       </c>
       <c r="T94">
-        <v>9.330657738733908</v>
+        <v>10.66360884426732</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03121992112222509</v>
+        <v>0.03088422304564202</v>
       </c>
       <c r="W94">
-        <v>0.2284383425993793</v>
+        <v>0.2285175002058376</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1836465948366183</v>
+        <v>0.1816719002684825</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2480486735984032</v>
+        <v>0.2499486735984032</v>
       </c>
       <c r="C95">
-        <v>-78.21666736927368</v>
+        <v>-79.42635878526841</v>
       </c>
       <c r="D95">
-        <v>17.02315345227658</v>
+        <v>16.86518053973938</v>
       </c>
       <c r="E95">
-        <v>91.2379704757973</v>
+        <v>92.28968897925482</v>
       </c>
       <c r="F95">
-        <v>97.80982082155026</v>
+        <v>98.86153932500778</v>
       </c>
       <c r="G95">
         <v>2.57</v>
@@ -9065,37 +9065,37 @@
         <v>4.19</v>
       </c>
       <c r="M95">
-        <v>23.06355574972155</v>
+        <v>23.31155097283684</v>
       </c>
       <c r="N95">
-        <v>-18.87355574972155</v>
+        <v>-19.12155097283684</v>
       </c>
       <c r="O95">
-        <v>-3.208504477452665</v>
+        <v>-3.250663665382262</v>
       </c>
       <c r="P95">
-        <v>-15.66505127226889</v>
+        <v>-15.87088730745457</v>
       </c>
       <c r="Q95">
-        <v>-15.26505127226889</v>
+        <v>-15.47088730745457</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5075342629567751</v>
+        <v>0.5844899734495711</v>
       </c>
       <c r="T95">
-        <v>10.66360884426732</v>
+        <v>12.44087698497855</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03088422304564202</v>
+        <v>0.03055566748132669</v>
       </c>
       <c r="W95">
-        <v>0.2285175002058376</v>
+        <v>0.2285949736079032</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1816719002684825</v>
+        <v>0.1797392204783923</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2499486735984032</v>
+        <v>0.2518486735984032</v>
       </c>
       <c r="C96">
-        <v>-79.42635878526841</v>
+        <v>-80.63314521813624</v>
       </c>
       <c r="D96">
-        <v>16.86518053973938</v>
+        <v>16.71011261032908</v>
       </c>
       <c r="E96">
-        <v>92.28968897925482</v>
+        <v>93.34140748271236</v>
       </c>
       <c r="F96">
-        <v>98.86153932500778</v>
+        <v>99.91325782846532</v>
       </c>
       <c r="G96">
         <v>2.57</v>
@@ -9147,37 +9147,37 @@
         <v>4.19</v>
       </c>
       <c r="M96">
-        <v>23.31155097283684</v>
+        <v>23.55954619595212</v>
       </c>
       <c r="N96">
-        <v>-19.12155097283684</v>
+        <v>-19.36954619595213</v>
       </c>
       <c r="O96">
-        <v>-3.250663665382262</v>
+        <v>-3.292822853311862</v>
       </c>
       <c r="P96">
-        <v>-15.87088730745457</v>
+        <v>-16.07672334264026</v>
       </c>
       <c r="Q96">
-        <v>-15.47088730745457</v>
+        <v>-15.67672334264026</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5844899734495711</v>
+        <v>0.6922279681394856</v>
       </c>
       <c r="T96">
-        <v>12.44087698497855</v>
+        <v>14.92905238197426</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03055566748132669</v>
+        <v>0.03023402887626009</v>
       </c>
       <c r="W96">
-        <v>0.2285949736079032</v>
+        <v>0.2286708159909779</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1797392204783923</v>
+        <v>0.1778472286838828</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2518486735984032</v>
+        <v>0.2537486735984032</v>
       </c>
       <c r="C97">
-        <v>-80.63314521813624</v>
+        <v>-81.837106067961</v>
       </c>
       <c r="D97">
-        <v>16.71011261032908</v>
+        <v>16.55787026396185</v>
       </c>
       <c r="E97">
-        <v>93.34140748271236</v>
+        <v>94.39312598616988</v>
       </c>
       <c r="F97">
-        <v>99.91325782846532</v>
+        <v>100.9649763319228</v>
       </c>
       <c r="G97">
         <v>2.57</v>
@@ -9229,37 +9229,37 @@
         <v>4.19</v>
       </c>
       <c r="M97">
-        <v>23.55954619595212</v>
+        <v>23.80754141906741</v>
       </c>
       <c r="N97">
-        <v>-19.36954619595213</v>
+        <v>-19.61754141906741</v>
       </c>
       <c r="O97">
-        <v>-3.292822853311862</v>
+        <v>-3.33498204124146</v>
       </c>
       <c r="P97">
-        <v>-16.07672334264026</v>
+        <v>-16.28255937782595</v>
       </c>
       <c r="Q97">
-        <v>-15.67672334264026</v>
+        <v>-15.88255937782595</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6922279681394856</v>
+        <v>0.8538349601743573</v>
       </c>
       <c r="T97">
-        <v>14.92905238197426</v>
+        <v>18.66131547746784</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03023402887626009</v>
+        <v>0.02991909107546572</v>
       </c>
       <c r="W97">
-        <v>0.2286708159909779</v>
+        <v>0.2287450783244052</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1778472286838828</v>
+        <v>0.1759946533850923</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2537486735984032</v>
+        <v>0.2556486735984032</v>
       </c>
       <c r="C98">
-        <v>-81.837106067961</v>
+        <v>-83.03831786736106</v>
       </c>
       <c r="D98">
-        <v>16.55787026396185</v>
+        <v>16.4083769680193</v>
       </c>
       <c r="E98">
-        <v>94.39312598616988</v>
+        <v>95.4448444896274</v>
       </c>
       <c r="F98">
-        <v>100.9649763319228</v>
+        <v>102.0166948353804</v>
       </c>
       <c r="G98">
         <v>2.57</v>
@@ -9311,37 +9311,37 @@
         <v>4.19</v>
       </c>
       <c r="M98">
-        <v>23.80754141906741</v>
+        <v>24.05553664218269</v>
       </c>
       <c r="N98">
-        <v>-19.61754141906741</v>
+        <v>-19.86553664218269</v>
       </c>
       <c r="O98">
-        <v>-3.33498204124146</v>
+        <v>-3.377141229171058</v>
       </c>
       <c r="P98">
-        <v>-16.28255937782595</v>
+        <v>-16.48839541301163</v>
       </c>
       <c r="Q98">
-        <v>-15.88255937782595</v>
+        <v>-16.08839541301163</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8538349601743551</v>
+        <v>1.12317994689914</v>
       </c>
       <c r="T98">
-        <v>18.66131547746779</v>
+        <v>24.88175396995705</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02991909107546572</v>
+        <v>0.02961064683757431</v>
       </c>
       <c r="W98">
-        <v>0.2287450783244052</v>
+        <v>0.2288178094757</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1759946533850923</v>
+        <v>0.1741802755151431</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2556486735984032</v>
+        <v>0.2575486735984032</v>
       </c>
       <c r="C99">
-        <v>-83.03831786736106</v>
+        <v>-84.23685440977621</v>
       </c>
       <c r="D99">
-        <v>16.4083769680193</v>
+        <v>16.26155892906168</v>
       </c>
       <c r="E99">
-        <v>95.4448444896274</v>
+        <v>96.49656299308494</v>
       </c>
       <c r="F99">
-        <v>102.0166948353804</v>
+        <v>103.0684133388379</v>
       </c>
       <c r="G99">
         <v>2.57</v>
@@ -9393,37 +9393,37 @@
         <v>4.19</v>
       </c>
       <c r="M99">
-        <v>24.05553664218269</v>
+        <v>24.30353186529798</v>
       </c>
       <c r="N99">
-        <v>-19.86553664218269</v>
+        <v>-20.11353186529798</v>
       </c>
       <c r="O99">
-        <v>-3.377141229171058</v>
+        <v>-3.419300417100657</v>
       </c>
       <c r="P99">
-        <v>-16.48839541301163</v>
+        <v>-16.69423144819732</v>
       </c>
       <c r="Q99">
-        <v>-16.08839541301163</v>
+        <v>-16.29423144819732</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.12317994689914</v>
+        <v>1.66186992034871</v>
       </c>
       <c r="T99">
-        <v>24.88175396995705</v>
+        <v>37.32263095493558</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02961064683757431</v>
+        <v>0.02930849738004805</v>
       </c>
       <c r="W99">
-        <v>0.2288178094757</v>
+        <v>0.2288890563177847</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1741802755151431</v>
+        <v>0.1724029257649884</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2575486735984032</v>
+        <v>0.2594486735984032</v>
       </c>
       <c r="C100">
-        <v>-84.23685440977621</v>
+        <v>-85.43278687092814</v>
       </c>
       <c r="D100">
-        <v>16.26155892906168</v>
+        <v>16.11734497136728</v>
       </c>
       <c r="E100">
-        <v>96.49656299308494</v>
+        <v>97.54828149654246</v>
       </c>
       <c r="F100">
-        <v>103.0684133388379</v>
+        <v>104.1201318422954</v>
       </c>
       <c r="G100">
         <v>2.57</v>
@@ -9475,37 +9475,37 @@
         <v>4.19</v>
       </c>
       <c r="M100">
-        <v>24.30353186529798</v>
+        <v>24.55152708841326</v>
       </c>
       <c r="N100">
-        <v>-20.11353186529798</v>
+        <v>-20.36152708841326</v>
       </c>
       <c r="O100">
-        <v>-3.419300417100657</v>
+        <v>-3.461459605030255</v>
       </c>
       <c r="P100">
-        <v>-16.69423144819732</v>
+        <v>-16.900067483383</v>
       </c>
       <c r="Q100">
-        <v>-16.29423144819732</v>
+        <v>-16.50006748338301</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.66186992034871</v>
+        <v>3.277939840697421</v>
       </c>
       <c r="T100">
-        <v>37.32263095493558</v>
+        <v>74.64526190987115</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02930849738004805</v>
+        <v>0.02901245195196675</v>
       </c>
       <c r="W100">
-        <v>0.2288890563177847</v>
+        <v>0.2289588638297262</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1724029257649884</v>
+        <v>0.1706614820703928</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2594486735984032</v>
-      </c>
-      <c r="C101">
-        <v>-85.43278687092814</v>
-      </c>
-      <c r="D101">
-        <v>16.11734497136728</v>
-      </c>
-      <c r="E101">
-        <v>97.54828149654246</v>
-      </c>
-      <c r="F101">
-        <v>104.1201318422954</v>
-      </c>
-      <c r="G101">
-        <v>2.57</v>
-      </c>
-      <c r="H101">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>4.59</v>
-      </c>
-      <c r="K101">
-        <v>0.4000000000000004</v>
-      </c>
-      <c r="L101">
-        <v>4.19</v>
-      </c>
-      <c r="M101">
-        <v>24.55152708841326</v>
-      </c>
-      <c r="N101">
-        <v>-20.36152708841326</v>
-      </c>
-      <c r="O101">
-        <v>-3.461459605030255</v>
-      </c>
-      <c r="P101">
-        <v>-16.900067483383</v>
-      </c>
-      <c r="Q101">
-        <v>-16.50006748338301</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.277939840697421</v>
-      </c>
-      <c r="T101">
-        <v>74.64526190987115</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02901245195196675</v>
-      </c>
-      <c r="W101">
-        <v>0.2289588638297262</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1706614820703928</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
